--- a/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
+++ b/reports/MASTER_LIVE_BACKLINKS_REPORT.xlsx
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1531</v>
+        <v>1647</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1289</v>
+        <v>1839</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>875</v>
+        <v>1042</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1401</v>
+        <v>1259</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>851</v>
+        <v>1202</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1008</v>
+        <v>917</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1382</v>
+        <v>1448</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>722</v>
+        <v>1182</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1189</v>
+        <v>1088</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1169</v>
+        <v>1148</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>812</v>
+        <v>1059</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1157</v>
+        <v>1088</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>758</v>
+        <v>1038</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>741</v>
+        <v>1313</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>718</v>
+        <v>981</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>696</v>
+        <v>1105</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>677</v>
+        <v>1029</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>683</v>
+        <v>1002</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>783</v>
+        <v>1072</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1110</v>
+        <v>1062</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>637</v>
+        <v>998</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>750</v>
+        <v>1027</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>647</v>
+        <v>972</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>659</v>
+        <v>978</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>786</v>
+        <v>1080</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>698</v>
+        <v>888</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>760</v>
+        <v>1012</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1106</v>
+        <v>1054</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>978</v>
+        <v>1041</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>706</v>
+        <v>1237</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>746</v>
+        <v>1026</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>671</v>
+        <v>980</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>728</v>
+        <v>1196</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>837</v>
+        <v>1002</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>647</v>
+        <v>1015</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>780</v>
+        <v>1010</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>662</v>
+        <v>809</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>911</v>
+        <v>951</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>751</v>
+        <v>871</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>733</v>
+        <v>900</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>978</v>
+        <v>899</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1186</v>
+        <v>800</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1174</v>
+        <v>993</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1192</v>
+        <v>907</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>840</v>
+        <v>1021</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>687</v>
+        <v>925</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>775</v>
+        <v>871</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>669</v>
+        <v>973</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>854</v>
+        <v>924</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>854</v>
+        <v>923</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>893</v>
+        <v>863</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>697</v>
+        <v>926</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>740</v>
+        <v>954</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>851</v>
+        <v>881</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>697</v>
+        <v>856</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>824</v>
+        <v>1110</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>849</v>
+        <v>894</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1571</v>
+        <v>912</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>864</v>
+        <v>979</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>744</v>
+        <v>834</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>584</v>
+        <v>768</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>673</v>
+        <v>764</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>736</v>
+        <v>839</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>594</v>
+        <v>738</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>643</v>
+        <v>718</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>747</v>
+        <v>853</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1105</v>
+        <v>873</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>614</v>
+        <v>770</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>646</v>
+        <v>783</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>697</v>
+        <v>862</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>707</v>
+        <v>868</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1708</v>
+        <v>770</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>766</v>
+        <v>829</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>603</v>
+        <v>747</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>878</v>
+        <v>916</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1196</v>
+        <v>797</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>775</v>
+        <v>885</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1767</v>
+        <v>940</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>650</v>
+        <v>781</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1057</v>
+        <v>832</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>665</v>
+        <v>811</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>713</v>
+        <v>833</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1041</v>
+        <v>736</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>765</v>
+        <v>740</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>767</v>
+        <v>878</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>789</v>
+        <v>914</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>877</v>
+        <v>741</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>651</v>
+        <v>888</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1866</v>
+        <v>801</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>853</v>
+        <v>735</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>604</v>
+        <v>723</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>619</v>
+        <v>749</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1191</v>
+        <v>696</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>579</v>
+        <v>801</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>689</v>
+        <v>715</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>866</v>
+        <v>733</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>608</v>
+        <v>708</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1282</v>
+        <v>719</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>654</v>
+        <v>710</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>621</v>
+        <v>771</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>620</v>
+        <v>763</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1399</v>
+        <v>797</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1180</v>
+        <v>763</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1169</v>
+        <v>967</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1332</v>
+        <v>692</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1220</v>
+        <v>736</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>624</v>
+        <v>709</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>387</v>
+        <v>572</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>386</v>
+        <v>302</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>686</v>
+        <v>273</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1392</v>
+        <v>279</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>374</v>
+        <v>249</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>368</v>
+        <v>266</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>389</v>
+        <v>269</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>382</v>
+        <v>266</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>368</v>
+        <v>260</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>357</v>
+        <v>585</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>423</v>
+        <v>263</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>457</v>
+        <v>263</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>373</v>
+        <v>259</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>377</v>
+        <v>262</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>387</v>
+        <v>285</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>656</v>
+        <v>325</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>456</v>
+        <v>311</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>372</v>
+        <v>267</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>371</v>
+        <v>304</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>377</v>
+        <v>275</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>370</v>
+        <v>275</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>367</v>
+        <v>274</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>389</v>
+        <v>265</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>421</v>
+        <v>572</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>381</v>
+        <v>256</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>394</v>
+        <v>262</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>383</v>
+        <v>263</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1599</v>
+        <v>458</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>388</v>
+        <v>777</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>386</v>
+        <v>461</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>653</v>
+        <v>419</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>501</v>
+        <v>411</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>436</v>
+        <v>562</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>391</v>
+        <v>453</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>400</v>
+        <v>807</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>377</v>
+        <v>719</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>366</v>
+        <v>427</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>388</v>
+        <v>786</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>382</v>
+        <v>910</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>403</v>
+        <v>443</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="n">
-        <v>374</v>
+        <v>317</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="n">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n">
-        <v>1153</v>
+        <v>1333</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n">
-        <v>323</v>
+        <v>960</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>270</v>
+        <v>341</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>621</v>
+        <v>936</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>342</v>
+        <v>1042</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>272</v>
+        <v>370</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>328</v>
+        <v>904</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="n">
-        <v>656</v>
+        <v>1015</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="n">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="I190" s="2" t="n">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>430</v>
+        <v>389</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>603</v>
+        <v>756</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>446</v>
+        <v>384</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="n">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>420</v>
+        <v>723</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>862</v>
+        <v>1221</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n">
-        <v>321</v>
+        <v>964</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n">
-        <v>312</v>
+        <v>695</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n">
-        <v>863</v>
+        <v>1185</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n">
-        <v>346</v>
+        <v>680</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n">
-        <v>384</v>
+        <v>265</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n">
-        <v>920</v>
+        <v>723</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n">
-        <v>324</v>
+        <v>593</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n">
-        <v>319</v>
+        <v>819</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>312</v>
+        <v>566</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n">
-        <v>285</v>
+        <v>593</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n">
-        <v>321</v>
+        <v>593</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n">
-        <v>553</v>
+        <v>595</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="n">
-        <v>176</v>
+        <v>263</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="I221" s="2" t="n">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="n">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="n">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n">
-        <v>415</v>
+        <v>732</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="n">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="I229" s="2" t="n">
-        <v>434</v>
+        <v>393</v>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="n">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n">
-        <v>727</v>
+        <v>691</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>319</v>
+        <v>554</v>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>633</v>
+        <v>877</v>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>643</v>
+        <v>764</v>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>307</v>
+        <v>554</v>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="n">
-        <v>572</v>
+        <v>709</v>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="I239" s="2" t="n">
-        <v>805</v>
+        <v>723</v>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="n">
-        <v>1670</v>
+        <v>754</v>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>853</v>
+        <v>795</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>594</v>
+        <v>751</v>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>639</v>
+        <v>810</v>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>638</v>
+        <v>729</v>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="I248" s="2" t="n">
-        <v>1100</v>
+        <v>828</v>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="n">
-        <v>795</v>
+        <v>768</v>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="n">
-        <v>1237</v>
+        <v>770</v>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="n">
-        <v>688</v>
+        <v>757</v>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="n">
-        <v>1007</v>
+        <v>703</v>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="n">
-        <v>600</v>
+        <v>762</v>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="I254" s="2" t="n">
-        <v>1742</v>
+        <v>731</v>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="n">
-        <v>736</v>
+        <v>1298</v>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="I256" s="2" t="n">
-        <v>752</v>
+        <v>732</v>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="n">
-        <v>713</v>
+        <v>935</v>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="I258" s="2" t="n">
-        <v>734</v>
+        <v>866</v>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="n">
-        <v>752</v>
+        <v>857</v>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="n">
-        <v>725</v>
+        <v>1026</v>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="n">
-        <v>683</v>
+        <v>893</v>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="n">
-        <v>709</v>
+        <v>849</v>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="n">
-        <v>868</v>
+        <v>1119</v>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n">
-        <v>702</v>
+        <v>1322</v>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n">
-        <v>708</v>
+        <v>1122</v>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>1306</v>
+        <v>1220</v>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="n">
-        <v>649</v>
+        <v>1076</v>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="n">
-        <v>677</v>
+        <v>911</v>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="I269" s="2" t="n">
-        <v>683</v>
+        <v>913</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="n">
-        <v>855</v>
+        <v>884</v>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="n">
-        <v>661</v>
+        <v>908</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="I272" s="2" t="n">
-        <v>783</v>
+        <v>818</v>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="n">
-        <v>648</v>
+        <v>1412</v>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="n">
-        <v>1457</v>
+        <v>1245</v>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="I275" s="2" t="n">
-        <v>835</v>
+        <v>1143</v>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="n">
-        <v>742</v>
+        <v>918</v>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="n">
-        <v>818</v>
+        <v>993</v>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="n">
-        <v>1026</v>
+        <v>922</v>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="n">
-        <v>644</v>
+        <v>853</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="I280" s="2" t="n">
-        <v>643</v>
+        <v>916</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="n">
-        <v>741</v>
+        <v>856</v>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="n">
-        <v>768</v>
+        <v>855</v>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n">
-        <v>878</v>
+        <v>820</v>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n">
-        <v>635</v>
+        <v>773</v>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="n">
-        <v>641</v>
+        <v>1107</v>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="n">
-        <v>718</v>
+        <v>1125</v>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="n">
-        <v>730</v>
+        <v>1820</v>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="I289" s="2" t="n">
-        <v>667</v>
+        <v>1170</v>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         </is>
       </c>
       <c r="I290" s="2" t="n">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="I291" s="2" t="n">
-        <v>645</v>
+        <v>855</v>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="I292" s="2" t="n">
-        <v>685</v>
+        <v>1750</v>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="n">
-        <v>1449</v>
+        <v>1756</v>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         </is>
       </c>
       <c r="I294" s="2" t="n">
-        <v>649</v>
+        <v>1782</v>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>645</v>
+        <v>840</v>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="n">
-        <v>1048</v>
+        <v>752</v>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n">
-        <v>676</v>
+        <v>724</v>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n">
-        <v>721</v>
+        <v>806</v>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="I300" s="2" t="n">
-        <v>617</v>
+        <v>805</v>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>639</v>
+        <v>760</v>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="I302" s="2" t="n">
-        <v>662</v>
+        <v>692</v>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="I303" s="2" t="n">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="I304" s="2" t="n">
-        <v>611</v>
+        <v>887</v>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="I305" s="2" t="n">
-        <v>843</v>
+        <v>761</v>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="I306" s="2" t="n">
-        <v>692</v>
+        <v>785</v>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="I307" s="2" t="n">
-        <v>923</v>
+        <v>826</v>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         </is>
       </c>
       <c r="I308" s="2" t="n">
-        <v>661</v>
+        <v>754</v>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         </is>
       </c>
       <c r="I309" s="2" t="n">
-        <v>715</v>
+        <v>791</v>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="I310" s="2" t="n">
-        <v>799</v>
+        <v>777</v>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="I311" s="2" t="n">
-        <v>725</v>
+        <v>801</v>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         </is>
       </c>
       <c r="I312" s="2" t="n">
-        <v>701</v>
+        <v>815</v>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="I313" s="2" t="n">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="I314" s="2" t="n">
-        <v>873</v>
+        <v>808</v>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="I315" s="2" t="n">
-        <v>991</v>
+        <v>840</v>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="I316" s="2" t="n">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="I317" s="2" t="n">
-        <v>657</v>
+        <v>794</v>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="I318" s="2" t="n">
-        <v>398</v>
+        <v>264</v>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         </is>
       </c>
       <c r="I319" s="2" t="n">
-        <v>401</v>
+        <v>283</v>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="I320" s="2" t="n">
-        <v>387</v>
+        <v>597</v>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         </is>
       </c>
       <c r="I321" s="2" t="n">
-        <v>375</v>
+        <v>242</v>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="I322" s="2" t="n">
-        <v>509</v>
+        <v>247</v>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="I323" s="2" t="n">
-        <v>388</v>
+        <v>644</v>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="I324" s="2" t="n">
-        <v>419</v>
+        <v>273</v>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="I325" s="2" t="n">
-        <v>399</v>
+        <v>275</v>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="I326" s="2" t="n">
-        <v>361</v>
+        <v>632</v>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="I327" s="2" t="n">
-        <v>417</v>
+        <v>267</v>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="I328" s="2" t="n">
-        <v>353</v>
+        <v>290</v>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="I329" s="2" t="n">
-        <v>374</v>
+        <v>261</v>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         </is>
       </c>
       <c r="I330" s="2" t="n">
-        <v>364</v>
+        <v>269</v>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         </is>
       </c>
       <c r="I331" s="2" t="n">
-        <v>372</v>
+        <v>257</v>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="I332" s="2" t="n">
-        <v>393</v>
+        <v>264</v>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         </is>
       </c>
       <c r="I333" s="2" t="n">
-        <v>361</v>
+        <v>239</v>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="I334" s="2" t="n">
-        <v>386</v>
+        <v>260</v>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         </is>
       </c>
       <c r="I335" s="2" t="n">
-        <v>375</v>
+        <v>270</v>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         </is>
       </c>
       <c r="I336" s="2" t="n">
-        <v>358</v>
+        <v>274</v>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="I337" s="2" t="n">
-        <v>363</v>
+        <v>272</v>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         </is>
       </c>
       <c r="I338" s="2" t="n">
-        <v>357</v>
+        <v>259</v>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="I339" s="2" t="n">
-        <v>369</v>
+        <v>260</v>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="I340" s="2" t="n">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="J340" s="4" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="I341" s="2" t="n">
-        <v>363</v>
+        <v>240</v>
       </c>
       <c r="J341" s="4" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="I342" s="2" t="n">
-        <v>365</v>
+        <v>265</v>
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         </is>
       </c>
       <c r="I343" s="2" t="n">
-        <v>1377</v>
+        <v>280</v>
       </c>
       <c r="J343" s="4" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         </is>
       </c>
       <c r="I344" s="2" t="n">
-        <v>366</v>
+        <v>257</v>
       </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="I345" s="2" t="n">
-        <v>668</v>
+        <v>266</v>
       </c>
       <c r="J345" s="4" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         </is>
       </c>
       <c r="I346" s="2" t="n">
-        <v>369</v>
+        <v>264</v>
       </c>
       <c r="J346" s="4" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         </is>
       </c>
       <c r="I347" s="2" t="n">
-        <v>382</v>
+        <v>264</v>
       </c>
       <c r="J347" s="4" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         </is>
       </c>
       <c r="I348" s="2" t="n">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="J348" s="4" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="I349" s="2" t="n">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="J349" s="4" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="I350" s="2" t="n">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="J350" s="4" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="I351" s="2" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J351" s="4" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="I352" s="2" t="n">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="J352" s="4" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="I353" s="2" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="J353" s="4" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         </is>
       </c>
       <c r="I354" s="2" t="n">
-        <v>433</v>
+        <v>394</v>
       </c>
       <c r="J354" s="4" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="I355" s="2" t="n">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="J355" s="4" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="I356" s="2" t="n">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="J356" s="4" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="I357" s="2" t="n">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="J357" s="4" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I358" s="2" t="n">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="J358" s="4" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="I359" s="2" t="n">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="J359" s="4" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="I360" s="2" t="n">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="J360" s="4" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         </is>
       </c>
       <c r="I361" s="2" t="n">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="J361" s="4" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         </is>
       </c>
       <c r="I362" s="2" t="n">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="J362" s="4" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         </is>
       </c>
       <c r="I363" s="2" t="n">
-        <v>372</v>
+        <v>788</v>
       </c>
       <c r="J363" s="4" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         </is>
       </c>
       <c r="I364" s="2" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="J364" s="4" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="I365" s="2" t="n">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="J365" s="4" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="I366" s="2" t="n">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="J366" s="4" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="I367" s="2" t="n">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="J367" s="4" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         </is>
       </c>
       <c r="I368" s="2" t="n">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="J368" s="4" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         </is>
       </c>
       <c r="I369" s="2" t="n">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="J369" s="4" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="I370" s="2" t="n">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="J370" s="4" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         </is>
       </c>
       <c r="I371" s="2" t="n">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="J371" s="4" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         </is>
       </c>
       <c r="I372" s="2" t="n">
-        <v>721</v>
+        <v>429</v>
       </c>
       <c r="J372" s="4" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="I373" s="2" t="n">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="J373" s="4" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         </is>
       </c>
       <c r="I374" s="2" t="n">
-        <v>1438</v>
+        <v>749</v>
       </c>
       <c r="J374" s="4" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         </is>
       </c>
       <c r="I375" s="2" t="n">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="J375" s="4" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="I376" s="2" t="n">
-        <v>402</v>
+        <v>727</v>
       </c>
       <c r="J376" s="4" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         </is>
       </c>
       <c r="I377" s="2" t="n">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="J377" s="4" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         </is>
       </c>
       <c r="I378" s="2" t="n">
-        <v>725</v>
+        <v>451</v>
       </c>
       <c r="J378" s="4" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="I379" s="2" t="n">
-        <v>653</v>
+        <v>452</v>
       </c>
       <c r="J379" s="4" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         </is>
       </c>
       <c r="I380" s="2" t="n">
-        <v>671</v>
+        <v>480</v>
       </c>
       <c r="J380" s="4" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         </is>
       </c>
       <c r="I381" s="2" t="n">
-        <v>607</v>
+        <v>1491</v>
       </c>
       <c r="J381" s="4" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         </is>
       </c>
       <c r="I382" s="2" t="n">
-        <v>584</v>
+        <v>411</v>
       </c>
       <c r="J382" s="4" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="I383" s="2" t="n">
-        <v>612</v>
+        <v>443</v>
       </c>
       <c r="J383" s="4" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         </is>
       </c>
       <c r="I384" s="2" t="n">
-        <v>573</v>
+        <v>439</v>
       </c>
       <c r="J384" s="4" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         </is>
       </c>
       <c r="I385" s="2" t="n">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="J385" s="4" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         </is>
       </c>
       <c r="I386" s="2" t="n">
-        <v>1449</v>
+        <v>457</v>
       </c>
       <c r="J386" s="4" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         </is>
       </c>
       <c r="I387" s="2" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J387" s="4" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         </is>
       </c>
       <c r="I388" s="2" t="n">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="J388" s="4" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="I389" s="2" t="n">
-        <v>468</v>
+        <v>419</v>
       </c>
       <c r="J389" s="4" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         </is>
       </c>
       <c r="I390" s="2" t="n">
-        <v>462</v>
+        <v>421</v>
       </c>
       <c r="J390" s="4" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         </is>
       </c>
       <c r="I391" s="2" t="n">
-        <v>1473</v>
+        <v>461</v>
       </c>
       <c r="J391" s="4" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="I392" s="2" t="n">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="J392" s="4" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="I393" s="2" t="n">
-        <v>567</v>
+        <v>1550</v>
       </c>
       <c r="J393" s="4" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         </is>
       </c>
       <c r="I394" s="2" t="n">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="J394" s="4" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         </is>
       </c>
       <c r="I395" s="2" t="n">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="J395" s="4" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         </is>
       </c>
       <c r="I396" s="2" t="n">
-        <v>456</v>
+        <v>421</v>
       </c>
       <c r="J396" s="4" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         </is>
       </c>
       <c r="I397" s="2" t="n">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="J397" s="4" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="I398" s="2" t="n">
-        <v>556</v>
+        <v>441</v>
       </c>
       <c r="J398" s="4" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         </is>
       </c>
       <c r="I399" s="2" t="n">
-        <v>482</v>
+        <v>443</v>
       </c>
       <c r="J399" s="4" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         </is>
       </c>
       <c r="I400" s="2" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J400" s="4" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="I401" s="2" t="n">
-        <v>572</v>
+        <v>431</v>
       </c>
       <c r="J401" s="4" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         </is>
       </c>
       <c r="I402" s="2" t="n">
-        <v>441</v>
+        <v>1486</v>
       </c>
       <c r="J402" s="4" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         </is>
       </c>
       <c r="I403" s="2" t="n">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="J403" s="4" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="I404" s="2" t="n">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="J404" s="4" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="I405" s="2" t="n">
-        <v>468</v>
+        <v>419</v>
       </c>
       <c r="J405" s="4" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="I406" s="2" t="n">
-        <v>500</v>
+        <v>1536</v>
       </c>
       <c r="J406" s="4" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         </is>
       </c>
       <c r="I407" s="2" t="n">
-        <v>822</v>
+        <v>421</v>
       </c>
       <c r="J407" s="4" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         </is>
       </c>
       <c r="I408" s="2" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="J408" s="4" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         </is>
       </c>
       <c r="I409" s="2" t="n">
-        <v>414</v>
+        <v>745</v>
       </c>
       <c r="J409" s="4" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         </is>
       </c>
       <c r="I410" s="2" t="n">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="J410" s="4" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         </is>
       </c>
       <c r="I411" s="2" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="J411" s="4" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         </is>
       </c>
       <c r="I412" s="2" t="n">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="J412" s="4" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="I413" s="2" t="n">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="J413" s="4" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         </is>
       </c>
       <c r="I414" s="2" t="n">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="J414" s="4" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         </is>
       </c>
       <c r="I415" s="2" t="n">
-        <v>439</v>
+        <v>747</v>
       </c>
       <c r="J415" s="4" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         </is>
       </c>
       <c r="I416" s="2" t="n">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="J416" s="4" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="I417" s="2" t="n">
-        <v>429</v>
+        <v>588</v>
       </c>
       <c r="J417" s="4" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         </is>
       </c>
       <c r="I418" s="2" t="n">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="J418" s="4" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         </is>
       </c>
       <c r="I419" s="2" t="n">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="J419" s="4" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         </is>
       </c>
       <c r="I420" s="2" t="n">
-        <v>826</v>
+        <v>394</v>
       </c>
       <c r="J420" s="4" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         </is>
       </c>
       <c r="I421" s="2" t="n">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="J421" s="4" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         </is>
       </c>
       <c r="I422" s="2" t="n">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="J422" s="4" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         </is>
       </c>
       <c r="I423" s="2" t="n">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="J423" s="4" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         </is>
       </c>
       <c r="I424" s="2" t="n">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="J424" s="4" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         </is>
       </c>
       <c r="I425" s="2" t="n">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="J425" s="4" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="I426" s="2" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="J426" s="4" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="I427" s="2" t="n">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="J427" s="4" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         </is>
       </c>
       <c r="I428" s="2" t="n">
-        <v>399</v>
+        <v>743</v>
       </c>
       <c r="J428" s="4" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         </is>
       </c>
       <c r="I429" s="2" t="n">
-        <v>426</v>
+        <v>741</v>
       </c>
       <c r="J429" s="4" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         </is>
       </c>
       <c r="I430" s="2" t="n">
-        <v>387</v>
+        <v>755</v>
       </c>
       <c r="J430" s="4" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         </is>
       </c>
       <c r="I431" s="2" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="J431" s="4" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         </is>
       </c>
       <c r="I432" s="2" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J432" s="4" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="I433" s="2" t="n">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="J433" s="4" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="I434" s="2" t="n">
-        <v>973</v>
+        <v>761</v>
       </c>
       <c r="J434" s="4" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         </is>
       </c>
       <c r="I435" s="2" t="n">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="J435" s="4" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         </is>
       </c>
       <c r="I436" s="2" t="n">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="J436" s="4" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="I437" s="2" t="n">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="J437" s="4" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         </is>
       </c>
       <c r="I438" s="2" t="n">
-        <v>845</v>
+        <v>324</v>
       </c>
       <c r="J438" s="4" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         </is>
       </c>
       <c r="I439" s="2" t="n">
-        <v>441</v>
+        <v>288</v>
       </c>
       <c r="J439" s="4" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         </is>
       </c>
       <c r="I440" s="2" t="n">
-        <v>377</v>
+        <v>291</v>
       </c>
       <c r="J440" s="4" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         </is>
       </c>
       <c r="I441" s="2" t="n">
-        <v>386</v>
+        <v>274</v>
       </c>
       <c r="J441" s="4" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="I442" s="2" t="n">
-        <v>389</v>
+        <v>278</v>
       </c>
       <c r="J442" s="4" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         </is>
       </c>
       <c r="I443" s="2" t="n">
-        <v>377</v>
+        <v>253</v>
       </c>
       <c r="J443" s="4" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="I444" s="2" t="n">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="J444" s="4" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         </is>
       </c>
       <c r="I445" s="2" t="n">
-        <v>376</v>
+        <v>634</v>
       </c>
       <c r="J445" s="4" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         </is>
       </c>
       <c r="I446" s="2" t="n">
-        <v>365</v>
+        <v>286</v>
       </c>
       <c r="J446" s="4" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         </is>
       </c>
       <c r="I447" s="2" t="n">
-        <v>372</v>
+        <v>287</v>
       </c>
       <c r="J447" s="4" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         </is>
       </c>
       <c r="I448" s="2" t="n">
-        <v>424</v>
+        <v>302</v>
       </c>
       <c r="J448" s="4" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         </is>
       </c>
       <c r="I449" s="2" t="n">
-        <v>381</v>
+        <v>251</v>
       </c>
       <c r="J449" s="4" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="I450" s="2" t="n">
-        <v>361</v>
+        <v>272</v>
       </c>
       <c r="J450" s="4" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         </is>
       </c>
       <c r="I451" s="2" t="n">
-        <v>366</v>
+        <v>288</v>
       </c>
       <c r="J451" s="4" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         </is>
       </c>
       <c r="I452" s="2" t="n">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="J452" s="4" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         </is>
       </c>
       <c r="I453" s="2" t="n">
-        <v>376</v>
+        <v>251</v>
       </c>
       <c r="J453" s="4" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="I454" s="2" t="n">
-        <v>370</v>
+        <v>245</v>
       </c>
       <c r="J454" s="4" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         </is>
       </c>
       <c r="I455" s="2" t="n">
-        <v>373</v>
+        <v>243</v>
       </c>
       <c r="J455" s="4" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         </is>
       </c>
       <c r="I456" s="2" t="n">
-        <v>357</v>
+        <v>268</v>
       </c>
       <c r="J456" s="4" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         </is>
       </c>
       <c r="I457" s="2" t="n">
-        <v>366</v>
+        <v>620</v>
       </c>
       <c r="J457" s="4" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         </is>
       </c>
       <c r="I458" s="2" t="n">
-        <v>357</v>
+        <v>617</v>
       </c>
       <c r="J458" s="4" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         </is>
       </c>
       <c r="I459" s="2" t="n">
-        <v>385</v>
+        <v>299</v>
       </c>
       <c r="J459" s="4" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         </is>
       </c>
       <c r="I460" s="2" t="n">
-        <v>366</v>
+        <v>266</v>
       </c>
       <c r="J460" s="4" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         </is>
       </c>
       <c r="I461" s="2" t="n">
-        <v>355</v>
+        <v>276</v>
       </c>
       <c r="J461" s="4" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         </is>
       </c>
       <c r="I462" s="2" t="n">
-        <v>361</v>
+        <v>326</v>
       </c>
       <c r="J462" s="4" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="I463" s="2" t="n">
-        <v>415</v>
+        <v>254</v>
       </c>
       <c r="J463" s="4" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="I464" s="2" t="n">
-        <v>360</v>
+        <v>313</v>
       </c>
       <c r="J464" s="4" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         </is>
       </c>
       <c r="I465" s="2" t="n">
-        <v>361</v>
+        <v>251</v>
       </c>
       <c r="J465" s="4" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="I466" s="2" t="n">
-        <v>363</v>
+        <v>255</v>
       </c>
       <c r="J466" s="4" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="I467" s="2" t="n">
-        <v>358</v>
+        <v>581</v>
       </c>
       <c r="J467" s="4" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="I468" s="2" t="n">
-        <v>626</v>
+        <v>736</v>
       </c>
       <c r="J468" s="4" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         </is>
       </c>
       <c r="I469" s="2" t="n">
-        <v>639</v>
+        <v>737</v>
       </c>
       <c r="J469" s="4" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         </is>
       </c>
       <c r="I470" s="2" t="n">
-        <v>597</v>
+        <v>953</v>
       </c>
       <c r="J470" s="4" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         </is>
       </c>
       <c r="I471" s="2" t="n">
-        <v>577</v>
+        <v>869</v>
       </c>
       <c r="J471" s="4" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="I472" s="2" t="n">
-        <v>731</v>
+        <v>844</v>
       </c>
       <c r="J472" s="4" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         </is>
       </c>
       <c r="I473" s="2" t="n">
-        <v>652</v>
+        <v>882</v>
       </c>
       <c r="J473" s="4" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="I474" s="2" t="n">
-        <v>674</v>
+        <v>786</v>
       </c>
       <c r="J474" s="4" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="I475" s="2" t="n">
-        <v>577</v>
+        <v>789</v>
       </c>
       <c r="J475" s="4" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         </is>
       </c>
       <c r="I476" s="2" t="n">
-        <v>669</v>
+        <v>751</v>
       </c>
       <c r="J476" s="4" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         </is>
       </c>
       <c r="I477" s="2" t="n">
-        <v>638</v>
+        <v>788</v>
       </c>
       <c r="J477" s="4" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         </is>
       </c>
       <c r="I478" s="2" t="n">
-        <v>591</v>
+        <v>1367</v>
       </c>
       <c r="J478" s="4" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         </is>
       </c>
       <c r="I479" s="2" t="n">
-        <v>689</v>
+        <v>738</v>
       </c>
       <c r="J479" s="4" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         </is>
       </c>
       <c r="I480" s="2" t="n">
-        <v>641</v>
+        <v>702</v>
       </c>
       <c r="J480" s="4" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="I481" s="2" t="n">
-        <v>656</v>
+        <v>735</v>
       </c>
       <c r="J481" s="4" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="I482" s="2" t="n">
-        <v>634</v>
+        <v>819</v>
       </c>
       <c r="J482" s="4" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         </is>
       </c>
       <c r="I483" s="2" t="n">
-        <v>670</v>
+        <v>875</v>
       </c>
       <c r="J483" s="4" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         </is>
       </c>
       <c r="I484" s="2" t="n">
-        <v>764</v>
+        <v>800</v>
       </c>
       <c r="J484" s="4" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         </is>
       </c>
       <c r="I485" s="2" t="n">
-        <v>732</v>
+        <v>806</v>
       </c>
       <c r="J485" s="4" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         </is>
       </c>
       <c r="I486" s="2" t="n">
-        <v>824</v>
+        <v>695</v>
       </c>
       <c r="J486" s="4" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         </is>
       </c>
       <c r="I487" s="2" t="n">
-        <v>602</v>
+        <v>735</v>
       </c>
       <c r="J487" s="4" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         </is>
       </c>
       <c r="I488" s="2" t="n">
-        <v>757</v>
+        <v>641</v>
       </c>
       <c r="J488" s="4" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         </is>
       </c>
       <c r="I489" s="2" t="n">
-        <v>602</v>
+        <v>841</v>
       </c>
       <c r="J489" s="4" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         </is>
       </c>
       <c r="I490" s="2" t="n">
-        <v>1608</v>
+        <v>818</v>
       </c>
       <c r="J490" s="4" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         </is>
       </c>
       <c r="I491" s="2" t="n">
-        <v>1587</v>
+        <v>736</v>
       </c>
       <c r="J491" s="4" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="I492" s="2" t="n">
-        <v>597</v>
+        <v>712</v>
       </c>
       <c r="J492" s="4" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         </is>
       </c>
       <c r="I493" s="2" t="n">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="J493" s="4" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         </is>
       </c>
       <c r="I494" s="2" t="n">
-        <v>621</v>
+        <v>752</v>
       </c>
       <c r="J494" s="4" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         </is>
       </c>
       <c r="I495" s="2" t="n">
-        <v>580</v>
+        <v>699</v>
       </c>
       <c r="J495" s="4" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         </is>
       </c>
       <c r="I496" s="2" t="n">
-        <v>589</v>
+        <v>752</v>
       </c>
       <c r="J496" s="4" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         </is>
       </c>
       <c r="I497" s="2" t="n">
-        <v>643</v>
+        <v>750</v>
       </c>
       <c r="J497" s="4" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="I498" s="2" t="n">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="J498" s="4" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         </is>
       </c>
       <c r="I499" s="2" t="n">
-        <v>911</v>
+        <v>807</v>
       </c>
       <c r="J499" s="2" t="inlineStr">
         <is>
@@ -25990,15 +25990,15 @@
       </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I500" s="2" t="n">
-        <v>1068</v>
-      </c>
-      <c r="J500" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3955</v>
+      </c>
+      <c r="J500" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K500" s="3" t="inlineStr">
@@ -26045,7 +26045,7 @@
         </is>
       </c>
       <c r="I501" s="2" t="n">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="J501" s="4" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         </is>
       </c>
       <c r="I502" s="2" t="n">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="J502" s="4" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         </is>
       </c>
       <c r="I503" s="2" t="n">
-        <v>992</v>
+        <v>839</v>
       </c>
       <c r="J503" s="4" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         </is>
       </c>
       <c r="I504" s="2" t="n">
-        <v>1759</v>
+        <v>2029</v>
       </c>
       <c r="J504" s="4" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="I505" s="2" t="n">
-        <v>714</v>
+        <v>4731</v>
       </c>
       <c r="J505" s="4" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         </is>
       </c>
       <c r="I506" s="2" t="n">
-        <v>382</v>
+        <v>700</v>
       </c>
       <c r="J506" s="4" t="inlineStr">
         <is>
@@ -26347,11 +26347,11 @@
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I507" s="2" t="n">
-        <v>2730</v>
+        <v>13512</v>
       </c>
       <c r="J507" s="4" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         </is>
       </c>
       <c r="I508" s="2" t="n">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="J508" s="4" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         </is>
       </c>
       <c r="I509" s="2" t="n">
-        <v>6591</v>
+        <v>6485</v>
       </c>
       <c r="J509" s="4" t="inlineStr">
         <is>
@@ -26500,15 +26500,15 @@
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I510" s="2" t="n">
-        <v>862</v>
-      </c>
-      <c r="J510" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3699</v>
+      </c>
+      <c r="J510" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K510" s="3" t="inlineStr">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="I511" s="2" t="n">
-        <v>1060</v>
+        <v>1021</v>
       </c>
       <c r="J511" s="4" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         </is>
       </c>
       <c r="I512" s="2" t="n">
-        <v>683</v>
+        <v>1185</v>
       </c>
       <c r="J512" s="4" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         </is>
       </c>
       <c r="I513" s="2" t="n">
-        <v>646</v>
+        <v>559</v>
       </c>
       <c r="J513" s="4" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         </is>
       </c>
       <c r="I514" s="2" t="n">
-        <v>1998</v>
+        <v>2556</v>
       </c>
       <c r="J514" s="4" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         </is>
       </c>
       <c r="I515" s="2" t="n">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="J515" s="4" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         </is>
       </c>
       <c r="I516" s="2" t="n">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="J516" s="4" t="inlineStr">
         <is>
@@ -26857,11 +26857,11 @@
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I517" s="2" t="n">
-        <v>3230</v>
+        <v>9799</v>
       </c>
       <c r="J517" s="4" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         </is>
       </c>
       <c r="I518" s="2" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J518" s="4" t="inlineStr">
         <is>
@@ -26959,15 +26959,15 @@
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I519" s="2" t="n">
-        <v>6602</v>
-      </c>
-      <c r="J519" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>614</v>
+      </c>
+      <c r="J519" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K519" s="3" t="inlineStr">
@@ -27010,15 +27010,15 @@
       </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I520" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="J520" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3715</v>
+      </c>
+      <c r="J520" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K520" s="3" t="inlineStr">
@@ -27065,7 +27065,7 @@
         </is>
       </c>
       <c r="I521" s="2" t="n">
-        <v>1119</v>
+        <v>1029</v>
       </c>
       <c r="J521" s="4" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         </is>
       </c>
       <c r="I522" s="2" t="n">
-        <v>419</v>
+        <v>923</v>
       </c>
       <c r="J522" s="4" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         </is>
       </c>
       <c r="I523" s="2" t="n">
-        <v>365</v>
+        <v>549</v>
       </c>
       <c r="J523" s="4" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         </is>
       </c>
       <c r="I524" s="2" t="n">
-        <v>1463</v>
+        <v>1687</v>
       </c>
       <c r="J524" s="2" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         </is>
       </c>
       <c r="I525" s="2" t="n">
-        <v>779</v>
+        <v>1546</v>
       </c>
       <c r="J525" s="4" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         </is>
       </c>
       <c r="I526" s="2" t="n">
-        <v>387</v>
+        <v>543</v>
       </c>
       <c r="J526" s="4" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="I527" s="2" t="n">
-        <v>960</v>
+        <v>2067</v>
       </c>
       <c r="J527" s="4" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         </is>
       </c>
       <c r="I528" s="2" t="n">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="J528" s="4" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         </is>
       </c>
       <c r="I529" s="2" t="n">
-        <v>7859</v>
+        <v>6502</v>
       </c>
       <c r="J529" s="4" t="inlineStr">
         <is>
@@ -27520,15 +27520,15 @@
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I530" s="2" t="n">
-        <v>936</v>
-      </c>
-      <c r="J530" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3732</v>
+      </c>
+      <c r="J530" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K530" s="3" t="inlineStr">
@@ -27575,7 +27575,7 @@
         </is>
       </c>
       <c r="I531" s="2" t="n">
-        <v>1033</v>
+        <v>1070</v>
       </c>
       <c r="J531" s="4" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         </is>
       </c>
       <c r="I532" s="2" t="n">
-        <v>599</v>
+        <v>795</v>
       </c>
       <c r="J532" s="4" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         </is>
       </c>
       <c r="I533" s="2" t="n">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="J533" s="4" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         </is>
       </c>
       <c r="I534" s="2" t="n">
-        <v>1528</v>
+        <v>1382</v>
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="I535" s="2" t="n">
-        <v>665</v>
+        <v>1101</v>
       </c>
       <c r="J535" s="4" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         </is>
       </c>
       <c r="I536" s="2" t="n">
-        <v>402</v>
+        <v>548</v>
       </c>
       <c r="J536" s="4" t="inlineStr">
         <is>
@@ -27877,11 +27877,11 @@
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I537" s="2" t="n">
-        <v>870</v>
+        <v>9287</v>
       </c>
       <c r="J537" s="4" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="I538" s="2" t="n">
-        <v>185</v>
+        <v>261</v>
       </c>
       <c r="J538" s="4" t="inlineStr">
         <is>
@@ -27979,15 +27979,15 @@
       </c>
       <c r="H539" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I539" s="2" t="n">
-        <v>10606</v>
-      </c>
-      <c r="J539" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>675</v>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K539" s="3" t="inlineStr">
@@ -28030,15 +28030,15 @@
       </c>
       <c r="H540" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I540" s="2" t="n">
-        <v>858</v>
-      </c>
-      <c r="J540" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3706</v>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K540" s="3" t="inlineStr">
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I541" s="2" t="n">
-        <v>1080</v>
+        <v>1044</v>
       </c>
       <c r="J541" s="4" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         </is>
       </c>
       <c r="I542" s="2" t="n">
-        <v>1354</v>
+        <v>904</v>
       </c>
       <c r="J542" s="4" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         </is>
       </c>
       <c r="I543" s="2" t="n">
-        <v>1328</v>
+        <v>1155</v>
       </c>
       <c r="J543" s="4" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         </is>
       </c>
       <c r="I544" s="2" t="n">
-        <v>1336</v>
+        <v>1607</v>
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         </is>
       </c>
       <c r="I545" s="2" t="n">
-        <v>2004</v>
+        <v>1535</v>
       </c>
       <c r="J545" s="4" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         </is>
       </c>
       <c r="I546" s="2" t="n">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="J546" s="4" t="inlineStr">
         <is>
@@ -28387,11 +28387,11 @@
       </c>
       <c r="H547" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I547" s="2" t="n">
-        <v>2774</v>
+        <v>13124</v>
       </c>
       <c r="J547" s="4" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         </is>
       </c>
       <c r="I548" s="2" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J548" s="4" t="inlineStr">
         <is>
@@ -28489,15 +28489,15 @@
       </c>
       <c r="H549" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I549" s="2" t="n">
-        <v>7897</v>
-      </c>
-      <c r="J549" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6437</v>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K549" s="3" t="inlineStr">
@@ -28540,15 +28540,15 @@
       </c>
       <c r="H550" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I550" s="2" t="n">
-        <v>860</v>
-      </c>
-      <c r="J550" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3738</v>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K550" s="3" t="inlineStr">
@@ -28595,7 +28595,7 @@
         </is>
       </c>
       <c r="I551" s="2" t="n">
-        <v>1169</v>
+        <v>1037</v>
       </c>
       <c r="J551" s="4" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         </is>
       </c>
       <c r="I552" s="2" t="n">
-        <v>1066</v>
+        <v>973</v>
       </c>
       <c r="J552" s="4" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="I553" s="2" t="n">
-        <v>566</v>
+        <v>917</v>
       </c>
       <c r="J553" s="4" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         </is>
       </c>
       <c r="I554" s="2" t="n">
-        <v>2755</v>
+        <v>2954</v>
       </c>
       <c r="J554" s="4" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         </is>
       </c>
       <c r="I555" s="2" t="n">
-        <v>358</v>
+        <v>580</v>
       </c>
       <c r="J555" s="4" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         </is>
       </c>
       <c r="I556" s="2" t="n">
-        <v>1041</v>
+        <v>4955</v>
       </c>
       <c r="J556" s="4" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         </is>
       </c>
       <c r="I557" s="2" t="n">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="J557" s="4" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         </is>
       </c>
       <c r="I558" s="2" t="n">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="J558" s="2" t="inlineStr">
         <is>
@@ -28999,15 +28999,15 @@
       </c>
       <c r="H559" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I559" s="2" t="n">
-        <v>859</v>
-      </c>
-      <c r="J559" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3725</v>
+      </c>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K559" s="3" t="inlineStr">
@@ -29054,7 +29054,7 @@
         </is>
       </c>
       <c r="I560" s="2" t="n">
-        <v>1036</v>
+        <v>1059</v>
       </c>
       <c r="J560" s="4" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         </is>
       </c>
       <c r="I561" s="2" t="n">
-        <v>921</v>
+        <v>1639</v>
       </c>
       <c r="J561" s="4" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I562" s="2" t="n">
-        <v>584</v>
+        <v>846</v>
       </c>
       <c r="J562" s="4" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         </is>
       </c>
       <c r="I563" s="2" t="n">
-        <v>1614</v>
+        <v>2139</v>
       </c>
       <c r="J563" s="4" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         </is>
       </c>
       <c r="I564" s="2" t="n">
-        <v>349</v>
+        <v>565</v>
       </c>
       <c r="J564" s="4" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         </is>
       </c>
       <c r="I565" s="2" t="n">
-        <v>1155</v>
+        <v>9590</v>
       </c>
       <c r="J565" s="4" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         </is>
       </c>
       <c r="I566" s="2" t="n">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="J566" s="4" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         </is>
       </c>
       <c r="I567" s="2" t="n">
-        <v>2969</v>
+        <v>646</v>
       </c>
       <c r="J567" s="2" t="inlineStr">
         <is>
@@ -29458,15 +29458,15 @@
       </c>
       <c r="H568" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I568" s="2" t="n">
-        <v>858</v>
-      </c>
-      <c r="J568" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3721</v>
+      </c>
+      <c r="J568" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K568" s="3" t="inlineStr">
@@ -29513,7 +29513,7 @@
         </is>
       </c>
       <c r="I569" s="2" t="n">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="J569" s="4" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         </is>
       </c>
       <c r="I570" s="2" t="n">
-        <v>1481</v>
+        <v>1033</v>
       </c>
       <c r="J570" s="4" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         </is>
       </c>
       <c r="I571" s="2" t="n">
-        <v>848</v>
+        <v>1070</v>
       </c>
       <c r="J571" s="4" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="I572" s="2" t="n">
-        <v>1233</v>
+        <v>1667</v>
       </c>
       <c r="J572" s="2" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         </is>
       </c>
       <c r="I573" s="2" t="n">
-        <v>1150</v>
+        <v>767</v>
       </c>
       <c r="J573" s="4" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         </is>
       </c>
       <c r="I574" s="2" t="n">
-        <v>388</v>
+        <v>530</v>
       </c>
       <c r="J574" s="4" t="inlineStr">
         <is>
@@ -29815,11 +29815,11 @@
       </c>
       <c r="H575" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I575" s="2" t="n">
-        <v>2101</v>
+        <v>9119</v>
       </c>
       <c r="J575" s="4" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         </is>
       </c>
       <c r="I576" s="2" t="n">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="J576" s="4" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         </is>
       </c>
       <c r="I577" s="2" t="n">
-        <v>6646</v>
+        <v>6430</v>
       </c>
       <c r="J577" s="4" t="inlineStr">
         <is>
@@ -29968,15 +29968,15 @@
       </c>
       <c r="H578" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I578" s="2" t="n">
-        <v>861</v>
-      </c>
-      <c r="J578" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3738</v>
+      </c>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K578" s="3" t="inlineStr">
@@ -30023,7 +30023,7 @@
         </is>
       </c>
       <c r="I579" s="2" t="n">
-        <v>1020</v>
+        <v>1103</v>
       </c>
       <c r="J579" s="4" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         </is>
       </c>
       <c r="I580" s="2" t="n">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="J580" s="4" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         </is>
       </c>
       <c r="I581" s="2" t="n">
-        <v>510</v>
+        <v>906</v>
       </c>
       <c r="J581" s="4" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         </is>
       </c>
       <c r="I582" s="2" t="n">
-        <v>5544</v>
+        <v>851</v>
       </c>
       <c r="J582" s="4" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         </is>
       </c>
       <c r="I583" s="2" t="n">
-        <v>484</v>
+        <v>554</v>
       </c>
       <c r="J583" s="4" t="inlineStr">
         <is>
@@ -30274,11 +30274,11 @@
       </c>
       <c r="H584" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I584" s="2" t="n">
-        <v>3232</v>
+        <v>11968</v>
       </c>
       <c r="J584" s="4" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         </is>
       </c>
       <c r="I585" s="2" t="n">
-        <v>204</v>
+        <v>299</v>
       </c>
       <c r="J585" s="4" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         </is>
       </c>
       <c r="I586" s="2" t="n">
-        <v>3103</v>
+        <v>645</v>
       </c>
       <c r="J586" s="2" t="inlineStr">
         <is>
@@ -30427,15 +30427,15 @@
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I587" s="2" t="n">
-        <v>846</v>
-      </c>
-      <c r="J587" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3710</v>
+      </c>
+      <c r="J587" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K587" s="3" t="inlineStr">
@@ -30482,7 +30482,7 @@
         </is>
       </c>
       <c r="I588" s="2" t="n">
-        <v>1055</v>
+        <v>1098</v>
       </c>
       <c r="J588" s="4" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         </is>
       </c>
       <c r="I589" s="2" t="n">
-        <v>607</v>
+        <v>1130</v>
       </c>
       <c r="J589" s="4" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         </is>
       </c>
       <c r="I590" s="2" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J590" s="4" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         </is>
       </c>
       <c r="I591" s="2" t="n">
-        <v>1270</v>
+        <v>2060</v>
       </c>
       <c r="J591" s="2" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         </is>
       </c>
       <c r="I592" s="2" t="n">
-        <v>680</v>
+        <v>7547</v>
       </c>
       <c r="J592" s="4" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         </is>
       </c>
       <c r="I593" s="2" t="n">
-        <v>394</v>
+        <v>579</v>
       </c>
       <c r="J593" s="4" t="inlineStr">
         <is>
@@ -30784,11 +30784,11 @@
       </c>
       <c r="H594" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I594" s="2" t="n">
-        <v>1170</v>
+        <v>9145</v>
       </c>
       <c r="J594" s="4" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         </is>
       </c>
       <c r="I595" s="2" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="J595" s="4" t="inlineStr">
         <is>
@@ -30886,15 +30886,15 @@
       </c>
       <c r="H596" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I596" s="2" t="n">
-        <v>8266</v>
-      </c>
-      <c r="J596" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2828</v>
+      </c>
+      <c r="J596" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K596" s="3" t="inlineStr">
@@ -30937,15 +30937,15 @@
       </c>
       <c r="H597" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I597" s="2" t="n">
-        <v>854</v>
-      </c>
-      <c r="J597" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3749</v>
+      </c>
+      <c r="J597" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K597" s="3" t="inlineStr">
@@ -30992,7 +30992,7 @@
         </is>
       </c>
       <c r="I598" s="2" t="n">
-        <v>1368</v>
+        <v>1054</v>
       </c>
       <c r="J598" s="4" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         </is>
       </c>
       <c r="I599" s="2" t="n">
-        <v>1395</v>
+        <v>841</v>
       </c>
       <c r="J599" s="4" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         </is>
       </c>
       <c r="I600" s="2" t="n">
-        <v>1048</v>
+        <v>1319</v>
       </c>
       <c r="J600" s="4" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         </is>
       </c>
       <c r="I601" s="2" t="n">
-        <v>1382</v>
+        <v>1228</v>
       </c>
       <c r="J601" s="2" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         </is>
       </c>
       <c r="I602" s="2" t="n">
-        <v>1253</v>
+        <v>1373</v>
       </c>
       <c r="J602" s="4" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         </is>
       </c>
       <c r="I603" s="2" t="n">
-        <v>413</v>
+        <v>597</v>
       </c>
       <c r="J603" s="4" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         </is>
       </c>
       <c r="I604" s="2" t="n">
-        <v>995</v>
+        <v>5253</v>
       </c>
       <c r="J604" s="4" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="I605" s="2" t="n">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="J605" s="4" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         </is>
       </c>
       <c r="I606" s="2" t="n">
-        <v>6545</v>
+        <v>6487</v>
       </c>
       <c r="J606" s="4" t="inlineStr">
         <is>
@@ -31447,15 +31447,15 @@
       </c>
       <c r="H607" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I607" s="2" t="n">
-        <v>860</v>
-      </c>
-      <c r="J607" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3714</v>
+      </c>
+      <c r="J607" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K607" s="3" t="inlineStr">
@@ -31502,7 +31502,7 @@
         </is>
       </c>
       <c r="I608" s="2" t="n">
-        <v>1108</v>
+        <v>1057</v>
       </c>
       <c r="J608" s="4" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         </is>
       </c>
       <c r="I609" s="2" t="n">
-        <v>1185</v>
+        <v>1522</v>
       </c>
       <c r="J609" s="4" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         </is>
       </c>
       <c r="I610" s="2" t="n">
-        <v>598</v>
+        <v>1064</v>
       </c>
       <c r="J610" s="4" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         </is>
       </c>
       <c r="I611" s="2" t="n">
-        <v>549</v>
+        <v>1104</v>
       </c>
       <c r="J611" s="4" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         </is>
       </c>
       <c r="I612" s="2" t="n">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="J612" s="4" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         </is>
       </c>
       <c r="I613" s="2" t="n">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="J613" s="4" t="inlineStr">
         <is>
@@ -31804,15 +31804,15 @@
       </c>
       <c r="H614" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I614" s="2" t="n">
-        <v>6785</v>
-      </c>
-      <c r="J614" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>644</v>
+      </c>
+      <c r="J614" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K614" s="3" t="inlineStr">
@@ -31855,15 +31855,15 @@
       </c>
       <c r="H615" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I615" s="2" t="n">
-        <v>878</v>
-      </c>
-      <c r="J615" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3723</v>
+      </c>
+      <c r="J615" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K615" s="3" t="inlineStr">
@@ -31910,7 +31910,7 @@
         </is>
       </c>
       <c r="I616" s="2" t="n">
-        <v>1089</v>
+        <v>1061</v>
       </c>
       <c r="J616" s="4" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         </is>
       </c>
       <c r="I617" s="2" t="n">
-        <v>569</v>
+        <v>827</v>
       </c>
       <c r="J617" s="4" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         </is>
       </c>
       <c r="I618" s="2" t="n">
-        <v>317</v>
+        <v>591</v>
       </c>
       <c r="J618" s="4" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         </is>
       </c>
       <c r="I619" s="2" t="n">
-        <v>1552</v>
+        <v>1893</v>
       </c>
       <c r="J619" s="2" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="I620" s="2" t="n">
-        <v>1377</v>
+        <v>2424</v>
       </c>
       <c r="J620" s="4" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         </is>
       </c>
       <c r="I621" s="2" t="n">
-        <v>366</v>
+        <v>1074</v>
       </c>
       <c r="J621" s="4" t="inlineStr">
         <is>
@@ -32212,15 +32212,15 @@
       </c>
       <c r="H622" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I622" s="2" t="n">
-        <v>989</v>
-      </c>
-      <c r="J622" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>10956</v>
+      </c>
+      <c r="J622" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K622" s="3" t="inlineStr">
@@ -32267,7 +32267,7 @@
         </is>
       </c>
       <c r="I623" s="2" t="n">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="J623" s="4" t="inlineStr">
         <is>
@@ -32314,15 +32314,15 @@
       </c>
       <c r="H624" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I624" s="2" t="n">
-        <v>6896</v>
-      </c>
-      <c r="J624" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2809</v>
+      </c>
+      <c r="J624" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K624" s="3" t="inlineStr">
@@ -32365,15 +32365,15 @@
       </c>
       <c r="H625" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I625" s="2" t="n">
-        <v>831</v>
-      </c>
-      <c r="J625" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3702</v>
+      </c>
+      <c r="J625" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K625" s="3" t="inlineStr">
@@ -32420,7 +32420,7 @@
         </is>
       </c>
       <c r="I626" s="2" t="n">
-        <v>1024</v>
+        <v>1049</v>
       </c>
       <c r="J626" s="4" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         </is>
       </c>
       <c r="I627" s="2" t="n">
-        <v>945</v>
+        <v>1292</v>
       </c>
       <c r="J627" s="4" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         </is>
       </c>
       <c r="I628" s="2" t="n">
-        <v>529</v>
+        <v>861</v>
       </c>
       <c r="J628" s="4" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         </is>
       </c>
       <c r="I629" s="2" t="n">
-        <v>498</v>
+        <v>3391</v>
       </c>
       <c r="J629" s="4" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         </is>
       </c>
       <c r="I630" s="2" t="n">
-        <v>414</v>
+        <v>577</v>
       </c>
       <c r="J630" s="4" t="inlineStr">
         <is>
@@ -32671,15 +32671,15 @@
       </c>
       <c r="H631" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I631" s="2" t="n">
-        <v>862</v>
-      </c>
-      <c r="J631" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>10878</v>
+      </c>
+      <c r="J631" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K631" s="3" t="inlineStr">
@@ -32726,7 +32726,7 @@
         </is>
       </c>
       <c r="I632" s="2" t="n">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="J632" s="4" t="inlineStr">
         <is>
@@ -32773,15 +32773,15 @@
       </c>
       <c r="H633" s="2" t="inlineStr">
         <is>
-          <t>HTTP 429</t>
+          <t>HTTP 410</t>
         </is>
       </c>
       <c r="I633" s="2" t="n">
-        <v>6799</v>
-      </c>
-      <c r="J633" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>6407</v>
+      </c>
+      <c r="J633" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K633" s="3" t="inlineStr">
@@ -32824,15 +32824,15 @@
       </c>
       <c r="H634" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I634" s="2" t="n">
-        <v>855</v>
-      </c>
-      <c r="J634" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3744</v>
+      </c>
+      <c r="J634" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K634" s="3" t="inlineStr">
@@ -32879,7 +32879,7 @@
         </is>
       </c>
       <c r="I635" s="2" t="n">
-        <v>1017</v>
+        <v>1092</v>
       </c>
       <c r="J635" s="4" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         </is>
       </c>
       <c r="I636" s="2" t="n">
-        <v>928</v>
+        <v>1026</v>
       </c>
       <c r="J636" s="4" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         </is>
       </c>
       <c r="I637" s="2" t="n">
-        <v>542</v>
+        <v>1416</v>
       </c>
       <c r="J637" s="4" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         </is>
       </c>
       <c r="I638" s="2" t="n">
-        <v>722</v>
+        <v>4579</v>
       </c>
       <c r="J638" s="4" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         </is>
       </c>
       <c r="I639" s="2" t="n">
-        <v>359</v>
+        <v>572</v>
       </c>
       <c r="J639" s="4" t="inlineStr">
         <is>
@@ -33130,15 +33130,15 @@
       </c>
       <c r="H640" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I640" s="2" t="n">
-        <v>2653</v>
-      </c>
-      <c r="J640" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11471</v>
+      </c>
+      <c r="J640" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K640" s="3" t="inlineStr">
@@ -33185,7 +33185,7 @@
         </is>
       </c>
       <c r="I641" s="2" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="J641" s="4" t="inlineStr">
         <is>
@@ -33232,11 +33232,11 @@
       </c>
       <c r="H642" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I642" s="2" t="n">
-        <v>8275</v>
+        <v>6480</v>
       </c>
       <c r="J642" s="2" t="inlineStr">
         <is>
@@ -33283,15 +33283,15 @@
       </c>
       <c r="H643" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I643" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="J643" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3733</v>
+      </c>
+      <c r="J643" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K643" s="3" t="inlineStr">
@@ -33338,7 +33338,7 @@
         </is>
       </c>
       <c r="I644" s="2" t="n">
-        <v>1034</v>
+        <v>1144</v>
       </c>
       <c r="J644" s="4" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         </is>
       </c>
       <c r="I645" s="2" t="n">
-        <v>919</v>
+        <v>1400</v>
       </c>
       <c r="J645" s="4" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         </is>
       </c>
       <c r="I646" s="2" t="n">
-        <v>906</v>
+        <v>514</v>
       </c>
       <c r="J646" s="4" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         </is>
       </c>
       <c r="I647" s="2" t="n">
-        <v>1257</v>
+        <v>2758</v>
       </c>
       <c r="J647" s="4" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         </is>
       </c>
       <c r="I648" s="2" t="n">
-        <v>367</v>
+        <v>749</v>
       </c>
       <c r="J648" s="4" t="inlineStr">
         <is>
@@ -33589,15 +33589,15 @@
       </c>
       <c r="H649" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I649" s="2" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J649" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11947</v>
+      </c>
+      <c r="J649" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K649" s="3" t="inlineStr">
@@ -33644,7 +33644,7 @@
         </is>
       </c>
       <c r="I650" s="2" t="n">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="J650" s="4" t="inlineStr">
         <is>
@@ -33691,11 +33691,11 @@
       </c>
       <c r="H651" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I651" s="2" t="n">
-        <v>6574</v>
+        <v>657</v>
       </c>
       <c r="J651" s="2" t="inlineStr">
         <is>
@@ -33742,15 +33742,15 @@
       </c>
       <c r="H652" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I652" s="2" t="n">
-        <v>843</v>
-      </c>
-      <c r="J652" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3719</v>
+      </c>
+      <c r="J652" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K652" s="3" t="inlineStr">
@@ -33797,7 +33797,7 @@
         </is>
       </c>
       <c r="I653" s="2" t="n">
-        <v>1027</v>
+        <v>1803</v>
       </c>
       <c r="J653" s="4" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         </is>
       </c>
       <c r="I654" s="2" t="n">
-        <v>421</v>
+        <v>722</v>
       </c>
       <c r="J654" s="4" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         </is>
       </c>
       <c r="I655" s="2" t="n">
-        <v>323</v>
+        <v>663</v>
       </c>
       <c r="J655" s="4" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         </is>
       </c>
       <c r="I656" s="2" t="n">
-        <v>1385</v>
+        <v>2395</v>
       </c>
       <c r="J656" s="2" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="I657" s="2" t="n">
-        <v>489</v>
+        <v>2505</v>
       </c>
       <c r="J657" s="4" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         </is>
       </c>
       <c r="I658" s="2" t="n">
-        <v>369</v>
+        <v>619</v>
       </c>
       <c r="J658" s="4" t="inlineStr">
         <is>
@@ -34099,15 +34099,15 @@
       </c>
       <c r="H659" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I659" s="2" t="n">
-        <v>2349</v>
-      </c>
-      <c r="J659" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>12024</v>
+      </c>
+      <c r="J659" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K659" s="3" t="inlineStr">
@@ -34154,7 +34154,7 @@
         </is>
       </c>
       <c r="I660" s="2" t="n">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="J660" s="4" t="inlineStr">
         <is>
@@ -34201,11 +34201,11 @@
       </c>
       <c r="H661" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I661" s="2" t="n">
-        <v>7756</v>
+        <v>6526</v>
       </c>
       <c r="J661" s="2" t="inlineStr">
         <is>
@@ -34252,15 +34252,15 @@
       </c>
       <c r="H662" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I662" s="2" t="n">
-        <v>890</v>
-      </c>
-      <c r="J662" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3728</v>
+      </c>
+      <c r="J662" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K662" s="3" t="inlineStr">
@@ -34307,7 +34307,7 @@
         </is>
       </c>
       <c r="I663" s="2" t="n">
-        <v>1383</v>
+        <v>2303</v>
       </c>
       <c r="J663" s="4" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         </is>
       </c>
       <c r="I664" s="2" t="n">
-        <v>979</v>
+        <v>903</v>
       </c>
       <c r="J664" s="4" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         </is>
       </c>
       <c r="I665" s="2" t="n">
-        <v>531</v>
+        <v>639</v>
       </c>
       <c r="J665" s="4" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         </is>
       </c>
       <c r="I666" s="2" t="n">
-        <v>14993</v>
+        <v>1265</v>
       </c>
       <c r="J666" s="4" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         </is>
       </c>
       <c r="I667" s="2" t="n">
-        <v>390</v>
+        <v>598</v>
       </c>
       <c r="J667" s="4" t="inlineStr">
         <is>
@@ -34558,15 +34558,15 @@
       </c>
       <c r="H668" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I668" s="2" t="n">
-        <v>979</v>
-      </c>
-      <c r="J668" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>12012</v>
+      </c>
+      <c r="J668" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K668" s="3" t="inlineStr">
@@ -34613,7 +34613,7 @@
         </is>
       </c>
       <c r="I669" s="2" t="n">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="J669" s="4" t="inlineStr">
         <is>
@@ -34660,11 +34660,11 @@
       </c>
       <c r="H670" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I670" s="2" t="n">
-        <v>3853</v>
+        <v>6489</v>
       </c>
       <c r="J670" s="2" t="inlineStr">
         <is>
@@ -34711,15 +34711,15 @@
       </c>
       <c r="H671" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I671" s="2" t="n">
-        <v>888</v>
-      </c>
-      <c r="J671" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3738</v>
+      </c>
+      <c r="J671" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K671" s="3" t="inlineStr">
@@ -34766,7 +34766,7 @@
         </is>
       </c>
       <c r="I672" s="2" t="n">
-        <v>1056</v>
+        <v>1383</v>
       </c>
       <c r="J672" s="4" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         </is>
       </c>
       <c r="I673" s="2" t="n">
-        <v>1103</v>
+        <v>1715</v>
       </c>
       <c r="J673" s="4" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         </is>
       </c>
       <c r="I674" s="2" t="n">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="J674" s="4" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         </is>
       </c>
       <c r="I675" s="2" t="n">
-        <v>1225</v>
+        <v>2204</v>
       </c>
       <c r="J675" s="4" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         </is>
       </c>
       <c r="I676" s="2" t="n">
-        <v>354</v>
+        <v>571</v>
       </c>
       <c r="J676" s="4" t="inlineStr">
         <is>
@@ -35017,15 +35017,15 @@
       </c>
       <c r="H677" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I677" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="J677" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>12050</v>
+      </c>
+      <c r="J677" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K677" s="3" t="inlineStr">
@@ -35072,7 +35072,7 @@
         </is>
       </c>
       <c r="I678" s="2" t="n">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="J678" s="4" t="inlineStr">
         <is>
@@ -35119,11 +35119,11 @@
       </c>
       <c r="H679" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I679" s="2" t="n">
-        <v>3631</v>
+        <v>643</v>
       </c>
       <c r="J679" s="2" t="inlineStr">
         <is>
@@ -35170,15 +35170,15 @@
       </c>
       <c r="H680" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I680" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="J680" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3751</v>
+      </c>
+      <c r="J680" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K680" s="3" t="inlineStr">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="I681" s="2" t="n">
-        <v>1192</v>
+        <v>1173</v>
       </c>
       <c r="J681" s="4" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         </is>
       </c>
       <c r="I682" s="2" t="n">
-        <v>572</v>
+        <v>851</v>
       </c>
       <c r="J682" s="4" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         </is>
       </c>
       <c r="I683" s="2" t="n">
-        <v>282</v>
+        <v>556</v>
       </c>
       <c r="J683" s="4" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         </is>
       </c>
       <c r="I684" s="2" t="n">
-        <v>2317</v>
+        <v>2862</v>
       </c>
       <c r="J684" s="4" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         </is>
       </c>
       <c r="I685" s="2" t="n">
-        <v>391</v>
+        <v>562</v>
       </c>
       <c r="J685" s="4" t="inlineStr">
         <is>
@@ -35476,15 +35476,15 @@
       </c>
       <c r="H686" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I686" s="2" t="n">
-        <v>1242</v>
-      </c>
-      <c r="J686" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>12032</v>
+      </c>
+      <c r="J686" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K686" s="3" t="inlineStr">
@@ -35531,7 +35531,7 @@
         </is>
       </c>
       <c r="I687" s="2" t="n">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="J687" s="4" t="inlineStr">
         <is>
@@ -35578,15 +35578,15 @@
       </c>
       <c r="H688" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I688" s="2" t="n">
-        <v>683</v>
-      </c>
-      <c r="J688" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6531</v>
+      </c>
+      <c r="J688" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K688" s="3" t="inlineStr">
@@ -35629,15 +35629,15 @@
       </c>
       <c r="H689" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I689" s="2" t="n">
-        <v>858</v>
-      </c>
-      <c r="J689" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3755</v>
+      </c>
+      <c r="J689" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K689" s="3" t="inlineStr">
@@ -35684,7 +35684,7 @@
         </is>
       </c>
       <c r="I690" s="2" t="n">
-        <v>1059</v>
+        <v>1155</v>
       </c>
       <c r="J690" s="4" t="inlineStr">
         <is>
@@ -35731,15 +35731,15 @@
       </c>
       <c r="H691" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I691" s="2" t="n">
-        <v>2605</v>
-      </c>
-      <c r="J691" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>895</v>
+      </c>
+      <c r="J691" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K691" s="3" t="inlineStr">
@@ -35786,7 +35786,7 @@
         </is>
       </c>
       <c r="I692" s="2" t="n">
-        <v>915</v>
+        <v>851</v>
       </c>
       <c r="J692" s="4" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         </is>
       </c>
       <c r="I693" s="2" t="n">
-        <v>365</v>
+        <v>522</v>
       </c>
       <c r="J693" s="4" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="I694" s="2" t="n">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="J694" s="4" t="inlineStr">
         <is>
@@ -35935,15 +35935,15 @@
       </c>
       <c r="H695" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I695" s="2" t="n">
-        <v>697</v>
-      </c>
-      <c r="J695" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6453</v>
+      </c>
+      <c r="J695" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K695" s="3" t="inlineStr">
@@ -35986,15 +35986,15 @@
       </c>
       <c r="H696" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I696" s="2" t="n">
-        <v>843</v>
-      </c>
-      <c r="J696" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3762</v>
+      </c>
+      <c r="J696" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K696" s="3" t="inlineStr">
@@ -36041,7 +36041,7 @@
         </is>
       </c>
       <c r="I697" s="2" t="n">
-        <v>2162</v>
+        <v>1203</v>
       </c>
       <c r="J697" s="4" t="inlineStr">
         <is>
@@ -36088,15 +36088,15 @@
       </c>
       <c r="H698" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I698" s="2" t="n">
-        <v>2630</v>
-      </c>
-      <c r="J698" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>865</v>
+      </c>
+      <c r="J698" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K698" s="3" t="inlineStr">
@@ -36143,7 +36143,7 @@
         </is>
       </c>
       <c r="I699" s="2" t="n">
-        <v>585</v>
+        <v>968</v>
       </c>
       <c r="J699" s="4" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         </is>
       </c>
       <c r="I700" s="2" t="n">
-        <v>357</v>
+        <v>542</v>
       </c>
       <c r="J700" s="4" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         </is>
       </c>
       <c r="I701" s="2" t="n">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="J701" s="4" t="inlineStr">
         <is>
@@ -36292,15 +36292,15 @@
       </c>
       <c r="H702" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I702" s="2" t="n">
-        <v>691</v>
-      </c>
-      <c r="J702" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6541</v>
+      </c>
+      <c r="J702" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K702" s="3" t="inlineStr">
@@ -36343,15 +36343,15 @@
       </c>
       <c r="H703" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I703" s="2" t="n">
-        <v>844</v>
-      </c>
-      <c r="J703" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3747</v>
+      </c>
+      <c r="J703" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K703" s="3" t="inlineStr">
@@ -36398,7 +36398,7 @@
         </is>
       </c>
       <c r="I704" s="2" t="n">
-        <v>1066</v>
+        <v>1105</v>
       </c>
       <c r="J704" s="4" t="inlineStr">
         <is>
@@ -36445,15 +36445,15 @@
       </c>
       <c r="H705" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I705" s="2" t="n">
-        <v>2635</v>
-      </c>
-      <c r="J705" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>1112</v>
+      </c>
+      <c r="J705" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K705" s="3" t="inlineStr">
@@ -36500,7 +36500,7 @@
         </is>
       </c>
       <c r="I706" s="2" t="n">
-        <v>560</v>
+        <v>897</v>
       </c>
       <c r="J706" s="4" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         </is>
       </c>
       <c r="I707" s="2" t="n">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="J707" s="4" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         </is>
       </c>
       <c r="I708" s="2" t="n">
-        <v>185</v>
+        <v>287</v>
       </c>
       <c r="J708" s="4" t="inlineStr">
         <is>
@@ -36649,15 +36649,15 @@
       </c>
       <c r="H709" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I709" s="2" t="n">
-        <v>707</v>
-      </c>
-      <c r="J709" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6556</v>
+      </c>
+      <c r="J709" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K709" s="3" t="inlineStr">
@@ -36700,15 +36700,15 @@
       </c>
       <c r="H710" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I710" s="2" t="n">
-        <v>881</v>
-      </c>
-      <c r="J710" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3748</v>
+      </c>
+      <c r="J710" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K710" s="3" t="inlineStr">
@@ -36755,7 +36755,7 @@
         </is>
       </c>
       <c r="I711" s="2" t="n">
-        <v>1088</v>
+        <v>1117</v>
       </c>
       <c r="J711" s="4" t="inlineStr">
         <is>
@@ -36802,15 +36802,15 @@
       </c>
       <c r="H712" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I712" s="2" t="n">
-        <v>2604</v>
-      </c>
-      <c r="J712" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>830</v>
+      </c>
+      <c r="J712" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K712" s="3" t="inlineStr">
@@ -36857,7 +36857,7 @@
         </is>
       </c>
       <c r="I713" s="2" t="n">
-        <v>1473</v>
+        <v>1651</v>
       </c>
       <c r="J713" s="4" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         </is>
       </c>
       <c r="I714" s="2" t="n">
-        <v>396</v>
+        <v>600</v>
       </c>
       <c r="J714" s="4" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         </is>
       </c>
       <c r="I715" s="2" t="n">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="J715" s="4" t="inlineStr">
         <is>
@@ -37006,15 +37006,15 @@
       </c>
       <c r="H716" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I716" s="2" t="n">
-        <v>665</v>
-      </c>
-      <c r="J716" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6478</v>
+      </c>
+      <c r="J716" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K716" s="3" t="inlineStr">
@@ -37057,15 +37057,15 @@
       </c>
       <c r="H717" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I717" s="2" t="n">
-        <v>842</v>
-      </c>
-      <c r="J717" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3727</v>
+      </c>
+      <c r="J717" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K717" s="3" t="inlineStr">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="I718" s="2" t="n">
-        <v>1051</v>
+        <v>1278</v>
       </c>
       <c r="J718" s="4" t="inlineStr">
         <is>
@@ -37159,15 +37159,15 @@
       </c>
       <c r="H719" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I719" s="2" t="n">
-        <v>2601</v>
-      </c>
-      <c r="J719" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>867</v>
+      </c>
+      <c r="J719" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K719" s="3" t="inlineStr">
@@ -37214,7 +37214,7 @@
         </is>
       </c>
       <c r="I720" s="2" t="n">
-        <v>1694</v>
+        <v>2527</v>
       </c>
       <c r="J720" s="4" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         </is>
       </c>
       <c r="I721" s="2" t="n">
-        <v>375</v>
+        <v>577</v>
       </c>
       <c r="J721" s="4" t="inlineStr">
         <is>
@@ -37312,15 +37312,15 @@
       </c>
       <c r="H722" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I722" s="2" t="n">
-        <v>653</v>
-      </c>
-      <c r="J722" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6483</v>
+      </c>
+      <c r="J722" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K722" s="3" t="inlineStr">
@@ -37363,15 +37363,15 @@
       </c>
       <c r="H723" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I723" s="2" t="n">
-        <v>835</v>
-      </c>
-      <c r="J723" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3740</v>
+      </c>
+      <c r="J723" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K723" s="3" t="inlineStr">
@@ -37418,7 +37418,7 @@
         </is>
       </c>
       <c r="I724" s="2" t="n">
-        <v>1089</v>
+        <v>1361</v>
       </c>
       <c r="J724" s="4" t="inlineStr">
         <is>
@@ -37465,15 +37465,15 @@
       </c>
       <c r="H725" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I725" s="2" t="n">
-        <v>2559</v>
-      </c>
-      <c r="J725" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>803</v>
+      </c>
+      <c r="J725" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K725" s="3" t="inlineStr">
@@ -37520,7 +37520,7 @@
         </is>
       </c>
       <c r="I726" s="2" t="n">
-        <v>582</v>
+        <v>2514</v>
       </c>
       <c r="J726" s="4" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="I727" s="2" t="n">
-        <v>392</v>
+        <v>569</v>
       </c>
       <c r="J727" s="4" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         </is>
       </c>
       <c r="I728" s="2" t="n">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="J728" s="4" t="inlineStr">
         <is>
@@ -37669,15 +37669,15 @@
       </c>
       <c r="H729" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 429</t>
         </is>
       </c>
       <c r="I729" s="2" t="n">
-        <v>742</v>
-      </c>
-      <c r="J729" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>6508</v>
+      </c>
+      <c r="J729" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K729" s="3" t="inlineStr">
@@ -37720,15 +37720,15 @@
       </c>
       <c r="H730" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I730" s="2" t="n">
-        <v>864</v>
-      </c>
-      <c r="J730" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3736</v>
+      </c>
+      <c r="J730" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K730" s="3" t="inlineStr">
@@ -37775,7 +37775,7 @@
         </is>
       </c>
       <c r="I731" s="2" t="n">
-        <v>1038</v>
+        <v>1094</v>
       </c>
       <c r="J731" s="4" t="inlineStr">
         <is>
@@ -37822,15 +37822,15 @@
       </c>
       <c r="H732" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I732" s="2" t="n">
-        <v>2695</v>
-      </c>
-      <c r="J732" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>1050</v>
+      </c>
+      <c r="J732" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K732" s="3" t="inlineStr">
@@ -37877,7 +37877,7 @@
         </is>
       </c>
       <c r="I733" s="2" t="n">
-        <v>491</v>
+        <v>1279</v>
       </c>
       <c r="J733" s="4" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         </is>
       </c>
       <c r="I734" s="2" t="n">
-        <v>380</v>
+        <v>592</v>
       </c>
       <c r="J734" s="4" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         </is>
       </c>
       <c r="I735" s="2" t="n">
-        <v>178</v>
+        <v>291</v>
       </c>
       <c r="J735" s="4" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         </is>
       </c>
       <c r="I736" s="2" t="n">
-        <v>700</v>
+        <v>6530</v>
       </c>
       <c r="J736" s="2" t="inlineStr">
         <is>
@@ -38077,15 +38077,15 @@
       </c>
       <c r="H737" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I737" s="2" t="n">
-        <v>870</v>
-      </c>
-      <c r="J737" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3720</v>
+      </c>
+      <c r="J737" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K737" s="3" t="inlineStr">
@@ -38132,7 +38132,7 @@
         </is>
       </c>
       <c r="I738" s="2" t="n">
-        <v>1111</v>
+        <v>1092</v>
       </c>
       <c r="J738" s="4" t="inlineStr">
         <is>
@@ -38179,15 +38179,15 @@
       </c>
       <c r="H739" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I739" s="2" t="n">
-        <v>2590</v>
-      </c>
-      <c r="J739" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>837</v>
+      </c>
+      <c r="J739" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K739" s="3" t="inlineStr">
@@ -38234,7 +38234,7 @@
         </is>
       </c>
       <c r="I740" s="2" t="n">
-        <v>485</v>
+        <v>1109</v>
       </c>
       <c r="J740" s="4" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         </is>
       </c>
       <c r="I741" s="2" t="n">
-        <v>404</v>
+        <v>622</v>
       </c>
       <c r="J741" s="4" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="I742" s="2" t="n">
-        <v>180</v>
+        <v>269</v>
       </c>
       <c r="J742" s="4" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         </is>
       </c>
       <c r="I743" s="2" t="n">
-        <v>749</v>
+        <v>8214</v>
       </c>
       <c r="J743" s="2" t="inlineStr">
         <is>
@@ -38434,15 +38434,15 @@
       </c>
       <c r="H744" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I744" s="2" t="n">
-        <v>837</v>
-      </c>
-      <c r="J744" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3701</v>
+      </c>
+      <c r="J744" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K744" s="3" t="inlineStr">
@@ -38489,7 +38489,7 @@
         </is>
       </c>
       <c r="I745" s="2" t="n">
-        <v>1052</v>
+        <v>1132</v>
       </c>
       <c r="J745" s="4" t="inlineStr">
         <is>
@@ -38536,15 +38536,15 @@
       </c>
       <c r="H746" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I746" s="2" t="n">
-        <v>2633</v>
-      </c>
-      <c r="J746" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>1154</v>
+      </c>
+      <c r="J746" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K746" s="3" t="inlineStr">
@@ -38591,7 +38591,7 @@
         </is>
       </c>
       <c r="I747" s="2" t="n">
-        <v>534</v>
+        <v>1210</v>
       </c>
       <c r="J747" s="4" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         </is>
       </c>
       <c r="I748" s="2" t="n">
-        <v>402</v>
+        <v>675</v>
       </c>
       <c r="J748" s="4" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         </is>
       </c>
       <c r="I749" s="2" t="n">
-        <v>214</v>
+        <v>298</v>
       </c>
       <c r="J749" s="4" t="inlineStr">
         <is>
@@ -38740,11 +38740,11 @@
       </c>
       <c r="H750" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400</t>
+          <t>HTTP 404</t>
         </is>
       </c>
       <c r="I750" s="2" t="n">
-        <v>724</v>
+        <v>2808</v>
       </c>
       <c r="J750" s="2" t="inlineStr">
         <is>
@@ -38791,15 +38791,15 @@
       </c>
       <c r="H751" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="I751" s="2" t="n">
-        <v>863</v>
-      </c>
-      <c r="J751" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3686</v>
+      </c>
+      <c r="J751" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="K751" s="3" t="inlineStr">
@@ -38846,7 +38846,7 @@
         </is>
       </c>
       <c r="I752" s="2" t="n">
-        <v>1075</v>
+        <v>1255</v>
       </c>
       <c r="J752" s="4" t="inlineStr">
         <is>
@@ -38893,15 +38893,15 @@
       </c>
       <c r="H753" s="2" t="inlineStr">
         <is>
-          <t>HTTP 0</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="I753" s="2" t="n">
-        <v>2682</v>
-      </c>
-      <c r="J753" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+        <v>1121</v>
+      </c>
+      <c r="J753" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="K753" s="3" t="inlineStr">
@@ -38948,7 +38948,7 @@
         </is>
       </c>
       <c r="I754" s="2" t="n">
-        <v>818</v>
+        <v>1607</v>
       </c>
       <c r="J754" s="4" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         </is>
       </c>
       <c r="I755" s="2" t="n">
-        <v>375</v>
+        <v>533</v>
       </c>
       <c r="J755" s="4" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         </is>
       </c>
       <c r="I756" s="2" t="n">
-        <v>738</v>
+        <v>799</v>
       </c>
       <c r="J756" s="4" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="I757" s="2" t="n">
-        <v>627</v>
+        <v>988</v>
       </c>
       <c r="J757" s="4" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         </is>
       </c>
       <c r="I758" s="2" t="n">
-        <v>726</v>
+        <v>845</v>
       </c>
       <c r="J758" s="4" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         </is>
       </c>
       <c r="I759" s="2" t="n">
-        <v>634</v>
+        <v>924</v>
       </c>
       <c r="J759" s="4" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         </is>
       </c>
       <c r="I760" s="2" t="n">
-        <v>692</v>
+        <v>859</v>
       </c>
       <c r="J760" s="4" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         </is>
       </c>
       <c r="I761" s="2" t="n">
-        <v>669</v>
+        <v>800</v>
       </c>
       <c r="J761" s="4" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         </is>
       </c>
       <c r="I762" s="2" t="n">
-        <v>684</v>
+        <v>832</v>
       </c>
       <c r="J762" s="4" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         </is>
       </c>
       <c r="I763" s="2" t="n">
-        <v>633</v>
+        <v>842</v>
       </c>
       <c r="J763" s="4" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="I764" s="2" t="n">
-        <v>1558</v>
+        <v>892</v>
       </c>
       <c r="J764" s="4" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         </is>
       </c>
       <c r="I765" s="2" t="n">
-        <v>735</v>
+        <v>891</v>
       </c>
       <c r="J765" s="4" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         </is>
       </c>
       <c r="I766" s="2" t="n">
-        <v>952</v>
+        <v>813</v>
       </c>
       <c r="J766" s="4" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         </is>
       </c>
       <c r="I767" s="2" t="n">
-        <v>667</v>
+        <v>813</v>
       </c>
       <c r="J767" s="4" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="I768" s="2" t="n">
-        <v>631</v>
+        <v>865</v>
       </c>
       <c r="J768" s="4" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         </is>
       </c>
       <c r="I769" s="2" t="n">
-        <v>837</v>
+        <v>860</v>
       </c>
       <c r="J769" s="4" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         </is>
       </c>
       <c r="I770" s="2" t="n">
-        <v>697</v>
+        <v>789</v>
       </c>
       <c r="J770" s="4" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         </is>
       </c>
       <c r="I771" s="2" t="n">
-        <v>659</v>
+        <v>780</v>
       </c>
       <c r="J771" s="4" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         </is>
       </c>
       <c r="I772" s="2" t="n">
-        <v>641</v>
+        <v>802</v>
       </c>
       <c r="J772" s="4" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         </is>
       </c>
       <c r="I773" s="2" t="n">
-        <v>683</v>
+        <v>910</v>
       </c>
       <c r="J773" s="4" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         </is>
       </c>
       <c r="I774" s="2" t="n">
-        <v>730</v>
+        <v>756</v>
       </c>
       <c r="J774" s="4" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         </is>
       </c>
       <c r="I775" s="2" t="n">
-        <v>753</v>
+        <v>789</v>
       </c>
       <c r="J775" s="4" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         </is>
       </c>
       <c r="I776" s="2" t="n">
-        <v>1668</v>
+        <v>753</v>
       </c>
       <c r="J776" s="4" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         </is>
       </c>
       <c r="I777" s="2" t="n">
-        <v>627</v>
+        <v>893</v>
       </c>
       <c r="J777" s="4" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         </is>
       </c>
       <c r="I778" s="2" t="n">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="J778" s="4" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="I779" s="2" t="n">
-        <v>751</v>
+        <v>989</v>
       </c>
       <c r="J779" s="4" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         </is>
       </c>
       <c r="I780" s="2" t="n">
-        <v>1790</v>
+        <v>807</v>
       </c>
       <c r="J780" s="4" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         </is>
       </c>
       <c r="I781" s="2" t="n">
-        <v>797</v>
+        <v>861</v>
       </c>
       <c r="J781" s="4" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         </is>
       </c>
       <c r="I782" s="2" t="n">
-        <v>754</v>
+        <v>826</v>
       </c>
       <c r="J782" s="4" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         </is>
       </c>
       <c r="I783" s="2" t="n">
-        <v>802</v>
+        <v>776</v>
       </c>
       <c r="J783" s="4" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         </is>
       </c>
       <c r="I784" s="2" t="n">
-        <v>961</v>
+        <v>833</v>
       </c>
       <c r="J784" s="4" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         </is>
       </c>
       <c r="I785" s="2" t="n">
-        <v>682</v>
+        <v>768</v>
       </c>
       <c r="J785" s="4" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         </is>
       </c>
       <c r="I786" s="2" t="n">
-        <v>1212</v>
+        <v>1179</v>
       </c>
       <c r="J786" s="4" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         </is>
       </c>
       <c r="I787" s="2" t="n">
-        <v>756</v>
+        <v>874</v>
       </c>
       <c r="J787" s="4" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         </is>
       </c>
       <c r="I788" s="2" t="n">
-        <v>631</v>
+        <v>739</v>
       </c>
       <c r="J788" s="4" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         </is>
       </c>
       <c r="I789" s="2" t="n">
-        <v>1616</v>
+        <v>766</v>
       </c>
       <c r="J789" s="4" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         </is>
       </c>
       <c r="I790" s="2" t="n">
-        <v>671</v>
+        <v>806</v>
       </c>
       <c r="J790" s="4" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         </is>
       </c>
       <c r="I791" s="2" t="n">
-        <v>649</v>
+        <v>768</v>
       </c>
       <c r="J791" s="4" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         </is>
       </c>
       <c r="I792" s="2" t="n">
-        <v>651</v>
+        <v>768</v>
       </c>
       <c r="J792" s="4" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         </is>
       </c>
       <c r="I793" s="2" t="n">
-        <v>699</v>
+        <v>754</v>
       </c>
       <c r="J793" s="4" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         </is>
       </c>
       <c r="I794" s="2" t="n">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="J794" s="4" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         </is>
       </c>
       <c r="I795" s="2" t="n">
-        <v>615</v>
+        <v>816</v>
       </c>
       <c r="J795" s="4" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         </is>
       </c>
       <c r="I796" s="2" t="n">
-        <v>641</v>
+        <v>753</v>
       </c>
       <c r="J796" s="4" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         </is>
       </c>
       <c r="I797" s="2" t="n">
-        <v>667</v>
+        <v>754</v>
       </c>
       <c r="J797" s="4" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         </is>
       </c>
       <c r="I798" s="2" t="n">
-        <v>605</v>
+        <v>861</v>
       </c>
       <c r="J798" s="4" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         </is>
       </c>
       <c r="I799" s="2" t="n">
-        <v>1675</v>
+        <v>757</v>
       </c>
       <c r="J799" s="4" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         </is>
       </c>
       <c r="I800" s="2" t="n">
-        <v>754</v>
+        <v>795</v>
       </c>
       <c r="J800" s="4" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         </is>
       </c>
       <c r="I801" s="2" t="n">
-        <v>674</v>
+        <v>839</v>
       </c>
       <c r="J801" s="4" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         </is>
       </c>
       <c r="I802" s="2" t="n">
-        <v>819</v>
+        <v>723</v>
       </c>
       <c r="J802" s="4" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="I803" s="2" t="n">
-        <v>663</v>
+        <v>858</v>
       </c>
       <c r="J803" s="4" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         </is>
       </c>
       <c r="I804" s="2" t="n">
-        <v>692</v>
+        <v>732</v>
       </c>
       <c r="J804" s="4" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         </is>
       </c>
       <c r="I805" s="2" t="n">
-        <v>632</v>
+        <v>769</v>
       </c>
       <c r="J805" s="4" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         </is>
       </c>
       <c r="I806" s="2" t="n">
-        <v>689</v>
+        <v>747</v>
       </c>
       <c r="J806" s="4" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         </is>
       </c>
       <c r="I807" s="2" t="n">
-        <v>1843</v>
+        <v>1067</v>
       </c>
       <c r="J807" s="4" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         </is>
       </c>
       <c r="I808" s="2" t="n">
-        <v>612</v>
+        <v>891</v>
       </c>
       <c r="J808" s="4" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         </is>
       </c>
       <c r="I809" s="2" t="n">
-        <v>594</v>
+        <v>828</v>
       </c>
       <c r="J809" s="4" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         </is>
       </c>
       <c r="I810" s="2" t="n">
-        <v>763</v>
+        <v>734</v>
       </c>
       <c r="J810" s="4" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         </is>
       </c>
       <c r="I811" s="2" t="n">
-        <v>637</v>
+        <v>843</v>
       </c>
       <c r="J811" s="4" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         </is>
       </c>
       <c r="I812" s="2" t="n">
-        <v>635</v>
+        <v>780</v>
       </c>
       <c r="J812" s="4" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         </is>
       </c>
       <c r="I813" s="2" t="n">
-        <v>670</v>
+        <v>797</v>
       </c>
       <c r="J813" s="4" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         </is>
       </c>
       <c r="I814" s="2" t="n">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="J814" s="4" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         </is>
       </c>
       <c r="I815" s="2" t="n">
-        <v>661</v>
+        <v>807</v>
       </c>
       <c r="J815" s="4" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         </is>
       </c>
       <c r="I816" s="2" t="n">
-        <v>1640</v>
+        <v>1105</v>
       </c>
       <c r="J816" s="4" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         </is>
       </c>
       <c r="I817" s="2" t="n">
-        <v>834</v>
+        <v>2060</v>
       </c>
       <c r="J817" s="4" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         </is>
       </c>
       <c r="I818" s="2" t="n">
-        <v>1954</v>
+        <v>4016</v>
       </c>
       <c r="J818" s="4" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         </is>
       </c>
       <c r="I819" s="2" t="n">
-        <v>538</v>
+        <v>1795</v>
       </c>
       <c r="J819" s="4" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         </is>
       </c>
       <c r="I820" s="2" t="n">
-        <v>698</v>
+        <v>5291</v>
       </c>
       <c r="J820" s="4" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         </is>
       </c>
       <c r="I821" s="2" t="n">
-        <v>1076</v>
+        <v>4371</v>
       </c>
       <c r="J821" s="4" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         </is>
       </c>
       <c r="I822" s="2" t="n">
-        <v>526</v>
+        <v>1633</v>
       </c>
       <c r="J822" s="4" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="I823" s="2" t="n">
-        <v>1311</v>
+        <v>2212</v>
       </c>
       <c r="J823" s="4" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         </is>
       </c>
       <c r="I824" s="2" t="n">
-        <v>1111</v>
+        <v>2125</v>
       </c>
       <c r="J824" s="4" t="inlineStr">
         <is>
@@ -42569,7 +42569,7 @@
         </is>
       </c>
       <c r="I825" s="2" t="n">
-        <v>2144</v>
+        <v>2643</v>
       </c>
       <c r="J825" s="4" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         </is>
       </c>
       <c r="I826" s="2" t="n">
-        <v>2119</v>
+        <v>2163</v>
       </c>
       <c r="J826" s="4" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="I827" s="2" t="n">
-        <v>1175</v>
+        <v>2368</v>
       </c>
       <c r="J827" s="4" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         </is>
       </c>
       <c r="I828" s="2" t="n">
-        <v>751</v>
+        <v>1401</v>
       </c>
       <c r="J828" s="4" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         </is>
       </c>
       <c r="I829" s="2" t="n">
-        <v>1281</v>
+        <v>1405</v>
       </c>
       <c r="J829" s="4" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         </is>
       </c>
       <c r="I830" s="2" t="n">
-        <v>813</v>
+        <v>2188</v>
       </c>
       <c r="J830" s="4" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         </is>
       </c>
       <c r="I831" s="2" t="n">
-        <v>15202</v>
+        <v>2866</v>
       </c>
       <c r="J831" s="4" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         </is>
       </c>
       <c r="I832" s="2" t="n">
-        <v>590</v>
+        <v>1131</v>
       </c>
       <c r="J832" s="4" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         </is>
       </c>
       <c r="I833" s="2" t="n">
-        <v>1944</v>
+        <v>3233</v>
       </c>
       <c r="J833" s="4" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         </is>
       </c>
       <c r="I834" s="2" t="n">
-        <v>859</v>
+        <v>3259</v>
       </c>
       <c r="J834" s="4" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         </is>
       </c>
       <c r="I835" s="2" t="n">
-        <v>1402</v>
+        <v>1276</v>
       </c>
       <c r="J835" s="4" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         </is>
       </c>
       <c r="I836" s="2" t="n">
-        <v>904</v>
+        <v>7535</v>
       </c>
       <c r="J836" s="4" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         </is>
       </c>
       <c r="I837" s="2" t="n">
-        <v>531</v>
+        <v>838</v>
       </c>
       <c r="J837" s="4" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="I838" s="2" t="n">
-        <v>880</v>
+        <v>1909</v>
       </c>
       <c r="J838" s="4" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         </is>
       </c>
       <c r="I839" s="2" t="n">
-        <v>631</v>
+        <v>1290</v>
       </c>
       <c r="J839" s="4" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="I840" s="2" t="n">
-        <v>1767</v>
+        <v>3070</v>
       </c>
       <c r="J840" s="4" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         </is>
       </c>
       <c r="I841" s="2" t="n">
-        <v>450</v>
+        <v>2346</v>
       </c>
       <c r="J841" s="4" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         </is>
       </c>
       <c r="I842" s="2" t="n">
-        <v>1646</v>
+        <v>2228</v>
       </c>
       <c r="J842" s="4" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         </is>
       </c>
       <c r="I843" s="2" t="n">
-        <v>1070</v>
+        <v>2099</v>
       </c>
       <c r="J843" s="4" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         </is>
       </c>
       <c r="I844" s="2" t="n">
-        <v>1097</v>
+        <v>1451</v>
       </c>
       <c r="J844" s="4" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         </is>
       </c>
       <c r="I845" s="2" t="n">
-        <v>1197</v>
+        <v>3659</v>
       </c>
       <c r="J845" s="4" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         </is>
       </c>
       <c r="I846" s="2" t="n">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="J846" s="4" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         </is>
       </c>
       <c r="I847" s="2" t="n">
-        <v>417</v>
+        <v>596</v>
       </c>
       <c r="J847" s="4" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         </is>
       </c>
       <c r="I848" s="2" t="n">
-        <v>374</v>
+        <v>618</v>
       </c>
       <c r="J848" s="4" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         </is>
       </c>
       <c r="I849" s="2" t="n">
-        <v>382</v>
+        <v>446</v>
       </c>
       <c r="J849" s="4" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         </is>
       </c>
       <c r="I850" s="2" t="n">
-        <v>362</v>
+        <v>599</v>
       </c>
       <c r="J850" s="4" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         </is>
       </c>
       <c r="I851" s="2" t="n">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="J851" s="4" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         </is>
       </c>
       <c r="I852" s="2" t="n">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="J852" s="4" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         </is>
       </c>
       <c r="I853" s="2" t="n">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="J853" s="4" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         </is>
       </c>
       <c r="I854" s="2" t="n">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="J854" s="4" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         </is>
       </c>
       <c r="I855" s="2" t="n">
-        <v>357</v>
+        <v>605</v>
       </c>
       <c r="J855" s="4" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         </is>
       </c>
       <c r="I856" s="2" t="n">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="J856" s="4" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         </is>
       </c>
       <c r="I857" s="2" t="n">
-        <v>365</v>
+        <v>430</v>
       </c>
       <c r="J857" s="4" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         </is>
       </c>
       <c r="I858" s="2" t="n">
-        <v>336</v>
+        <v>411</v>
       </c>
       <c r="J858" s="4" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         </is>
       </c>
       <c r="I859" s="2" t="n">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J859" s="4" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         </is>
       </c>
       <c r="I860" s="2" t="n">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="J860" s="4" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         </is>
       </c>
       <c r="I861" s="2" t="n">
-        <v>372</v>
+        <v>552</v>
       </c>
       <c r="J861" s="4" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         </is>
       </c>
       <c r="I862" s="2" t="n">
-        <v>363</v>
+        <v>558</v>
       </c>
       <c r="J862" s="4" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         </is>
       </c>
       <c r="I863" s="2" t="n">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="J863" s="4" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="I864" s="2" t="n">
-        <v>411</v>
+        <v>585</v>
       </c>
       <c r="J864" s="4" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         </is>
       </c>
       <c r="I865" s="2" t="n">
-        <v>361</v>
+        <v>579</v>
       </c>
       <c r="J865" s="4" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         </is>
       </c>
       <c r="I866" s="2" t="n">
-        <v>395</v>
+        <v>610</v>
       </c>
       <c r="J866" s="4" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         </is>
       </c>
       <c r="I867" s="2" t="n">
-        <v>394</v>
+        <v>570</v>
       </c>
       <c r="J867" s="4" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         </is>
       </c>
       <c r="I868" s="2" t="n">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="J868" s="4" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         </is>
       </c>
       <c r="I869" s="2" t="n">
-        <v>392</v>
+        <v>459</v>
       </c>
       <c r="J869" s="4" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         </is>
       </c>
       <c r="I870" s="2" t="n">
-        <v>389</v>
+        <v>551</v>
       </c>
       <c r="J870" s="4" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         </is>
       </c>
       <c r="I871" s="2" t="n">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="J871" s="4" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         </is>
       </c>
       <c r="I872" s="2" t="n">
-        <v>362</v>
+        <v>576</v>
       </c>
       <c r="J872" s="4" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         </is>
       </c>
       <c r="I873" s="2" t="n">
-        <v>360</v>
+        <v>543</v>
       </c>
       <c r="J873" s="4" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         </is>
       </c>
       <c r="I874" s="2" t="n">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J874" s="4" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         </is>
       </c>
       <c r="I875" s="2" t="n">
-        <v>371</v>
+        <v>630</v>
       </c>
       <c r="J875" s="4" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         </is>
       </c>
       <c r="I876" s="2" t="n">
-        <v>1006</v>
+        <v>1345</v>
       </c>
       <c r="J876" s="4" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         </is>
       </c>
       <c r="I877" s="2" t="n">
-        <v>513</v>
+        <v>2250</v>
       </c>
       <c r="J877" s="4" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         </is>
       </c>
       <c r="I878" s="2" t="n">
-        <v>1093</v>
+        <v>1067</v>
       </c>
       <c r="J878" s="4" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         </is>
       </c>
       <c r="I879" s="2" t="n">
-        <v>595</v>
+        <v>2206</v>
       </c>
       <c r="J879" s="4" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         </is>
       </c>
       <c r="I880" s="2" t="n">
-        <v>1788</v>
+        <v>840</v>
       </c>
       <c r="J880" s="4" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         </is>
       </c>
       <c r="I881" s="2" t="n">
-        <v>971</v>
+        <v>839</v>
       </c>
       <c r="J881" s="4" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         </is>
       </c>
       <c r="I882" s="2" t="n">
-        <v>964</v>
+        <v>872</v>
       </c>
       <c r="J882" s="4" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         </is>
       </c>
       <c r="I883" s="2" t="n">
-        <v>3476</v>
+        <v>1224</v>
       </c>
       <c r="J883" s="4" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         </is>
       </c>
       <c r="I884" s="2" t="n">
-        <v>1855</v>
+        <v>4189</v>
       </c>
       <c r="J884" s="4" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         </is>
       </c>
       <c r="I885" s="2" t="n">
-        <v>545</v>
+        <v>662</v>
       </c>
       <c r="J885" s="4" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         </is>
       </c>
       <c r="I886" s="2" t="n">
-        <v>450</v>
+        <v>6374</v>
       </c>
       <c r="J886" s="4" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         </is>
       </c>
       <c r="I887" s="2" t="n">
-        <v>2247</v>
+        <v>6837</v>
       </c>
       <c r="J887" s="4" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         </is>
       </c>
       <c r="I888" s="2" t="n">
-        <v>2710</v>
+        <v>5470</v>
       </c>
       <c r="J888" s="4" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         </is>
       </c>
       <c r="I889" s="2" t="n">
-        <v>935</v>
+        <v>4377</v>
       </c>
       <c r="J889" s="4" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         </is>
       </c>
       <c r="I890" s="2" t="n">
-        <v>824</v>
+        <v>6710</v>
       </c>
       <c r="J890" s="4" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         </is>
       </c>
       <c r="I891" s="2" t="n">
-        <v>1363</v>
+        <v>4377</v>
       </c>
       <c r="J891" s="4" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         </is>
       </c>
       <c r="I892" s="2" t="n">
-        <v>3276</v>
+        <v>1533</v>
       </c>
       <c r="J892" s="4" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         </is>
       </c>
       <c r="I893" s="2" t="n">
-        <v>808</v>
+        <v>1442</v>
       </c>
       <c r="J893" s="4" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         </is>
       </c>
       <c r="I894" s="2" t="n">
-        <v>5983</v>
+        <v>8398</v>
       </c>
       <c r="J894" s="4" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         </is>
       </c>
       <c r="I895" s="2" t="n">
-        <v>473</v>
+        <v>828</v>
       </c>
       <c r="J895" s="4" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         </is>
       </c>
       <c r="I896" s="2" t="n">
-        <v>1166</v>
+        <v>2928</v>
       </c>
       <c r="J896" s="4" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         </is>
       </c>
       <c r="I897" s="2" t="n">
-        <v>3277</v>
+        <v>1131</v>
       </c>
       <c r="J897" s="4" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         </is>
       </c>
       <c r="I898" s="2" t="n">
-        <v>754</v>
+        <v>4221</v>
       </c>
       <c r="J898" s="4" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         </is>
       </c>
       <c r="I899" s="2" t="n">
-        <v>2051</v>
+        <v>2509</v>
       </c>
       <c r="J899" s="4" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         </is>
       </c>
       <c r="I900" s="2" t="n">
-        <v>1098</v>
+        <v>1434</v>
       </c>
       <c r="J900" s="4" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="I901" s="2" t="n">
-        <v>2804</v>
+        <v>1001</v>
       </c>
       <c r="J901" s="4" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         </is>
       </c>
       <c r="I902" s="2" t="n">
-        <v>1573</v>
+        <v>1769</v>
       </c>
       <c r="J902" s="4" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         </is>
       </c>
       <c r="I903" s="2" t="n">
-        <v>888</v>
+        <v>2288</v>
       </c>
       <c r="J903" s="4" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         </is>
       </c>
       <c r="I904" s="2" t="n">
-        <v>767</v>
+        <v>1160</v>
       </c>
       <c r="J904" s="4" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         </is>
       </c>
       <c r="I905" s="2" t="n">
-        <v>1621</v>
+        <v>4254</v>
       </c>
       <c r="J905" s="4" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         </is>
       </c>
       <c r="I906" s="2" t="n">
-        <v>539</v>
+        <v>407</v>
       </c>
       <c r="J906" s="4" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         </is>
       </c>
       <c r="I907" s="2" t="n">
-        <v>548</v>
+        <v>414</v>
       </c>
       <c r="J907" s="4" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         </is>
       </c>
       <c r="I908" s="2" t="n">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="J908" s="4" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         </is>
       </c>
       <c r="I909" s="2" t="n">
-        <v>596</v>
+        <v>467</v>
       </c>
       <c r="J909" s="4" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         </is>
       </c>
       <c r="I910" s="2" t="n">
-        <v>496</v>
+        <v>598</v>
       </c>
       <c r="J910" s="4" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         </is>
       </c>
       <c r="I911" s="2" t="n">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J911" s="4" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         </is>
       </c>
       <c r="I912" s="2" t="n">
-        <v>613</v>
+        <v>525</v>
       </c>
       <c r="J912" s="4" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         </is>
       </c>
       <c r="I913" s="2" t="n">
-        <v>538</v>
+        <v>393</v>
       </c>
       <c r="J913" s="4" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         </is>
       </c>
       <c r="I914" s="2" t="n">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="J914" s="4" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         </is>
       </c>
       <c r="I915" s="2" t="n">
-        <v>478</v>
+        <v>537</v>
       </c>
       <c r="J915" s="4" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         </is>
       </c>
       <c r="I916" s="2" t="n">
-        <v>605</v>
+        <v>532</v>
       </c>
       <c r="J916" s="4" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         </is>
       </c>
       <c r="I917" s="2" t="n">
-        <v>534</v>
+        <v>609</v>
       </c>
       <c r="J917" s="4" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         </is>
       </c>
       <c r="I918" s="2" t="n">
-        <v>547</v>
+        <v>445</v>
       </c>
       <c r="J918" s="4" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         </is>
       </c>
       <c r="I919" s="2" t="n">
-        <v>484</v>
+        <v>402</v>
       </c>
       <c r="J919" s="4" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         </is>
       </c>
       <c r="I920" s="2" t="n">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="J920" s="4" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         </is>
       </c>
       <c r="I921" s="2" t="n">
-        <v>488</v>
+        <v>556</v>
       </c>
       <c r="J921" s="4" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         </is>
       </c>
       <c r="I922" s="2" t="n">
-        <v>511</v>
+        <v>551</v>
       </c>
       <c r="J922" s="4" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         </is>
       </c>
       <c r="I923" s="2" t="n">
-        <v>572</v>
+        <v>397</v>
       </c>
       <c r="J923" s="4" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         </is>
       </c>
       <c r="I924" s="2" t="n">
-        <v>486</v>
+        <v>554</v>
       </c>
       <c r="J924" s="4" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="I925" s="2" t="n">
-        <v>498</v>
+        <v>549</v>
       </c>
       <c r="J925" s="4" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         </is>
       </c>
       <c r="I926" s="2" t="n">
-        <v>549</v>
+        <v>407</v>
       </c>
       <c r="J926" s="4" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         </is>
       </c>
       <c r="I927" s="2" t="n">
-        <v>541</v>
+        <v>373</v>
       </c>
       <c r="J927" s="4" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         </is>
       </c>
       <c r="I928" s="2" t="n">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="J928" s="4" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         </is>
       </c>
       <c r="I929" s="2" t="n">
-        <v>529</v>
+        <v>403</v>
       </c>
       <c r="J929" s="4" t="inlineStr">
         <is>
@@ -47924,7 +47924,7 @@
         </is>
       </c>
       <c r="I930" s="2" t="n">
-        <v>551</v>
+        <v>404</v>
       </c>
       <c r="J930" s="4" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="I931" s="2" t="n">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="J931" s="4" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         </is>
       </c>
       <c r="I932" s="2" t="n">
-        <v>495</v>
+        <v>391</v>
       </c>
       <c r="J932" s="4" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         </is>
       </c>
       <c r="I933" s="2" t="n">
-        <v>473</v>
+        <v>542</v>
       </c>
       <c r="J933" s="4" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         </is>
       </c>
       <c r="I934" s="2" t="n">
-        <v>470</v>
+        <v>522</v>
       </c>
       <c r="J934" s="4" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         </is>
       </c>
       <c r="I935" s="2" t="n">
-        <v>523</v>
+        <v>594</v>
       </c>
       <c r="J935" s="4" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         </is>
       </c>
       <c r="I936" s="2" t="n">
-        <v>2393</v>
+        <v>714</v>
       </c>
       <c r="J936" s="4" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         </is>
       </c>
       <c r="I937" s="2" t="n">
-        <v>615</v>
+        <v>798</v>
       </c>
       <c r="J937" s="4" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         </is>
       </c>
       <c r="I938" s="2" t="n">
-        <v>1913</v>
+        <v>784</v>
       </c>
       <c r="J938" s="4" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         </is>
       </c>
       <c r="I939" s="2" t="n">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="J939" s="4" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         </is>
       </c>
       <c r="I940" s="2" t="n">
-        <v>611</v>
+        <v>840</v>
       </c>
       <c r="J940" s="4" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         </is>
       </c>
       <c r="I941" s="2" t="n">
-        <v>608</v>
+        <v>764</v>
       </c>
       <c r="J941" s="4" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         </is>
       </c>
       <c r="I942" s="2" t="n">
-        <v>654</v>
+        <v>722</v>
       </c>
       <c r="J942" s="4" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         </is>
       </c>
       <c r="I943" s="2" t="n">
-        <v>576</v>
+        <v>808</v>
       </c>
       <c r="J943" s="4" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         </is>
       </c>
       <c r="I944" s="2" t="n">
-        <v>688</v>
+        <v>720</v>
       </c>
       <c r="J944" s="4" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         </is>
       </c>
       <c r="I945" s="2" t="n">
-        <v>887</v>
+        <v>737</v>
       </c>
       <c r="J945" s="4" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         </is>
       </c>
       <c r="I946" s="2" t="n">
-        <v>619</v>
+        <v>749</v>
       </c>
       <c r="J946" s="4" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         </is>
       </c>
       <c r="I947" s="2" t="n">
-        <v>2235</v>
+        <v>827</v>
       </c>
       <c r="J947" s="4" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         </is>
       </c>
       <c r="I948" s="2" t="n">
-        <v>595</v>
+        <v>796</v>
       </c>
       <c r="J948" s="4" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         </is>
       </c>
       <c r="I949" s="2" t="n">
-        <v>736</v>
+        <v>769</v>
       </c>
       <c r="J949" s="4" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         </is>
       </c>
       <c r="I950" s="2" t="n">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="J950" s="4" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         </is>
       </c>
       <c r="I951" s="2" t="n">
-        <v>676</v>
+        <v>1346</v>
       </c>
       <c r="J951" s="4" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         </is>
       </c>
       <c r="I952" s="2" t="n">
-        <v>594</v>
+        <v>733</v>
       </c>
       <c r="J952" s="4" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         </is>
       </c>
       <c r="I953" s="2" t="n">
-        <v>760</v>
+        <v>722</v>
       </c>
       <c r="J953" s="4" t="inlineStr">
         <is>
@@ -49148,7 +49148,7 @@
         </is>
       </c>
       <c r="I954" s="2" t="n">
-        <v>742</v>
+        <v>945</v>
       </c>
       <c r="J954" s="4" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         </is>
       </c>
       <c r="I955" s="2" t="n">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="J955" s="4" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         </is>
       </c>
       <c r="I956" s="2" t="n">
-        <v>1441</v>
+        <v>779</v>
       </c>
       <c r="J956" s="4" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         </is>
       </c>
       <c r="I957" s="2" t="n">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="J957" s="4" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         </is>
       </c>
       <c r="I958" s="2" t="n">
-        <v>2285</v>
+        <v>1206</v>
       </c>
       <c r="J958" s="4" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         </is>
       </c>
       <c r="I959" s="2" t="n">
-        <v>819</v>
+        <v>852</v>
       </c>
       <c r="J959" s="4" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         </is>
       </c>
       <c r="I960" s="2" t="n">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="J960" s="4" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         </is>
       </c>
       <c r="I961" s="2" t="n">
-        <v>1100</v>
+        <v>1194</v>
       </c>
       <c r="J961" s="4" t="inlineStr">
         <is>
@@ -49556,7 +49556,7 @@
         </is>
       </c>
       <c r="I962" s="2" t="n">
-        <v>686</v>
+        <v>745</v>
       </c>
       <c r="J962" s="4" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         </is>
       </c>
       <c r="I963" s="2" t="n">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="J963" s="4" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         </is>
       </c>
       <c r="I964" s="2" t="n">
-        <v>1098</v>
+        <v>1173</v>
       </c>
       <c r="J964" s="4" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         </is>
       </c>
       <c r="I965" s="2" t="n">
-        <v>615</v>
+        <v>762</v>
       </c>
       <c r="J965" s="4" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         </is>
       </c>
       <c r="I966" s="2" t="n">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="J966" s="4" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         </is>
       </c>
       <c r="I967" s="2" t="n">
-        <v>1105</v>
+        <v>1351</v>
       </c>
       <c r="J967" s="4" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         </is>
       </c>
       <c r="I968" s="2" t="n">
-        <v>801</v>
+        <v>872</v>
       </c>
       <c r="J968" s="4" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         </is>
       </c>
       <c r="I969" s="2" t="n">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="J969" s="4" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         </is>
       </c>
       <c r="I970" s="2" t="n">
-        <v>1069</v>
+        <v>1242</v>
       </c>
       <c r="J970" s="4" t="inlineStr">
         <is>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-09-28 09:56:59 UTC</t>
+          <t>2026-10-05 10:49:46 UTC</t>
         </is>
       </c>
     </row>
@@ -53145,7 +53145,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>96.2% (932/969 Verified HTTP 200/202)</t>
+          <t>93.3% (904/969 Verified HTTP 200/202)</t>
         </is>
       </c>
     </row>
@@ -53157,7 +53157,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>896 ms</t>
+          <t>1259 ms</t>
         </is>
       </c>
     </row>
